--- a/research/traditional_assets/database/data/morocco/morocco_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_retail_automotive.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1003334450792858</v>
+        <v>0.1000429780550321</v>
       </c>
       <c r="C2">
-        <v>1439.879441981919</v>
+        <v>1432.195503736012</v>
       </c>
       <c r="D2">
-        <v>1302.279441981919</v>
+        <v>1309.253049402137</v>
       </c>
       <c r="E2">
-        <v>-139.454566612507</v>
+        <v>-124.7970209463819</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14.65754566612507</v>
       </c>
       <c r="G2">
         <v>137.6</v>
@@ -1451,28 +1451,28 @@
         <v>84.63</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.737274547006091</v>
       </c>
       <c r="N2">
-        <v>84.63</v>
+        <v>83.8927254529939</v>
       </c>
       <c r="O2">
-        <v>27.0816</v>
+        <v>26.84567214495805</v>
       </c>
       <c r="P2">
-        <v>57.5484</v>
+        <v>57.04705330803586</v>
       </c>
       <c r="Q2">
-        <v>94.44839999999999</v>
+        <v>93.94705330803586</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1003334450792858</v>
+        <v>0.1007080182374062</v>
       </c>
       <c r="T2">
-        <v>0.7107536019307608</v>
+        <v>0.7156355458632145</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>114.7876328345577</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1000429780550321</v>
+        <v>0.09975251103077838</v>
       </c>
       <c r="C3">
-        <v>1432.195503736012</v>
+        <v>1424.586653857892</v>
       </c>
       <c r="D3">
-        <v>1309.253049402137</v>
+        <v>1316.301745190142</v>
       </c>
       <c r="E3">
-        <v>-124.7970209463819</v>
+        <v>-110.1394752802568</v>
       </c>
       <c r="F3">
-        <v>14.65754566612507</v>
+        <v>29.31509133225014</v>
       </c>
       <c r="G3">
         <v>137.6</v>
@@ -1533,28 +1533,28 @@
         <v>84.63</v>
       </c>
       <c r="M3">
-        <v>0.737274547006091</v>
+        <v>1.474549094012182</v>
       </c>
       <c r="N3">
-        <v>83.8927254529939</v>
+        <v>83.15545090598782</v>
       </c>
       <c r="O3">
-        <v>26.84567214495805</v>
+        <v>26.6097442899161</v>
       </c>
       <c r="P3">
-        <v>57.04705330803586</v>
+        <v>56.54570661607171</v>
       </c>
       <c r="Q3">
-        <v>93.94705330803586</v>
+        <v>93.4457066160717</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1007080182374062</v>
+        <v>0.1010902357456922</v>
       </c>
       <c r="T3">
-        <v>0.7156355458632145</v>
+        <v>0.7206171213044937</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>114.7876328345577</v>
+        <v>57.39381641727883</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09975251103077838</v>
+        <v>0.09946204400652467</v>
       </c>
       <c r="C4">
-        <v>1424.586653857892</v>
+        <v>1417.054111683972</v>
       </c>
       <c r="D4">
-        <v>1316.301745190142</v>
+        <v>1323.426748682347</v>
       </c>
       <c r="E4">
-        <v>-110.1394752802568</v>
+        <v>-95.48192961413179</v>
       </c>
       <c r="F4">
-        <v>29.31509133225014</v>
+        <v>43.97263699837521</v>
       </c>
       <c r="G4">
         <v>137.6</v>
@@ -1615,28 +1615,28 @@
         <v>84.63</v>
       </c>
       <c r="M4">
-        <v>1.474549094012182</v>
+        <v>2.211823641018273</v>
       </c>
       <c r="N4">
-        <v>83.15545090598782</v>
+        <v>82.41817635898173</v>
       </c>
       <c r="O4">
-        <v>26.6097442899161</v>
+        <v>26.37381643487415</v>
       </c>
       <c r="P4">
-        <v>56.54570661607171</v>
+        <v>56.04435992410757</v>
       </c>
       <c r="Q4">
-        <v>93.4457066160717</v>
+        <v>92.94435992410757</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1010902357456922</v>
+        <v>0.101480334027345</v>
       </c>
       <c r="T4">
-        <v>0.7206171213044937</v>
+        <v>0.7257014096414696</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>57.39381641727883</v>
+        <v>38.26254427818589</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09946204400652467</v>
+        <v>0.09917157698227096</v>
       </c>
       <c r="C5">
-        <v>1417.054111683972</v>
+        <v>1409.599123094907</v>
       </c>
       <c r="D5">
-        <v>1323.426748682347</v>
+        <v>1330.629305759407</v>
       </c>
       <c r="E5">
-        <v>-95.48192961413179</v>
+        <v>-80.82438394800671</v>
       </c>
       <c r="F5">
-        <v>43.97263699837521</v>
+        <v>58.63018266450028</v>
       </c>
       <c r="G5">
         <v>137.6</v>
@@ -1697,28 +1697,28 @@
         <v>84.63</v>
       </c>
       <c r="M5">
-        <v>2.211823641018273</v>
+        <v>2.949098188024364</v>
       </c>
       <c r="N5">
-        <v>82.41817635898173</v>
+        <v>81.68090181197563</v>
       </c>
       <c r="O5">
-        <v>26.37381643487415</v>
+        <v>26.1378885798322</v>
       </c>
       <c r="P5">
-        <v>56.04435992410757</v>
+        <v>55.54301323214342</v>
       </c>
       <c r="Q5">
-        <v>92.94435992410757</v>
+        <v>92.44301323214341</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.101480334027345</v>
+        <v>0.1018785593565323</v>
       </c>
       <c r="T5">
-        <v>0.7257014096414696</v>
+        <v>0.7308916206521323</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>38.26254427818589</v>
+        <v>28.69690820863942</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09917157698227096</v>
+        <v>0.09888110995801724</v>
       </c>
       <c r="C6">
-        <v>1409.599123094907</v>
+        <v>1402.222961241864</v>
       </c>
       <c r="D6">
-        <v>1330.629305759407</v>
+        <v>1337.910689572489</v>
       </c>
       <c r="E6">
-        <v>-80.82438394800671</v>
+        <v>-66.16683828188164</v>
       </c>
       <c r="F6">
-        <v>58.63018266450028</v>
+        <v>73.28772833062536</v>
       </c>
       <c r="G6">
         <v>137.6</v>
@@ -1779,28 +1779,28 @@
         <v>84.63</v>
       </c>
       <c r="M6">
-        <v>2.949098188024364</v>
+        <v>3.686372735030455</v>
       </c>
       <c r="N6">
-        <v>81.68090181197563</v>
+        <v>80.94362726496954</v>
       </c>
       <c r="O6">
-        <v>26.1378885798322</v>
+        <v>25.90196072479025</v>
       </c>
       <c r="P6">
-        <v>55.54301323214342</v>
+        <v>55.04166654017928</v>
       </c>
       <c r="Q6">
-        <v>92.44301323214341</v>
+        <v>91.94166654017928</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1018785593565323</v>
+        <v>0.1022851683768603</v>
       </c>
       <c r="T6">
-        <v>0.7308916206521323</v>
+        <v>0.7361910992630196</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>28.69690820863942</v>
+        <v>22.95752656691153</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09888110995801724</v>
+        <v>0.09859064293376352</v>
       </c>
       <c r="C7">
-        <v>1402.222961241864</v>
+        <v>1394.926927296764</v>
       </c>
       <c r="D7">
-        <v>1337.910689572489</v>
+        <v>1345.272201293515</v>
       </c>
       <c r="E7">
-        <v>-66.16683828188164</v>
+        <v>-51.50929261575656</v>
       </c>
       <c r="F7">
-        <v>73.28772833062536</v>
+        <v>87.94527399675043</v>
       </c>
       <c r="G7">
         <v>137.6</v>
@@ -1861,28 +1861,28 @@
         <v>84.63</v>
       </c>
       <c r="M7">
-        <v>3.686372735030455</v>
+        <v>4.423647282036546</v>
       </c>
       <c r="N7">
-        <v>80.94362726496954</v>
+        <v>80.20635271796345</v>
       </c>
       <c r="O7">
-        <v>25.90196072479025</v>
+        <v>25.66603286974831</v>
       </c>
       <c r="P7">
-        <v>55.04166654017928</v>
+        <v>54.54031984821515</v>
       </c>
       <c r="Q7">
-        <v>91.94166654017928</v>
+        <v>91.44031984821515</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1022851683768603</v>
+        <v>0.1027004286529399</v>
       </c>
       <c r="T7">
-        <v>0.7361910992630196</v>
+        <v>0.7416033327379682</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.95752656691153</v>
+        <v>19.13127213909295</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09859064293376352</v>
+        <v>0.09830017590950982</v>
       </c>
       <c r="C8">
-        <v>1394.926927296764</v>
+        <v>1387.712351227436</v>
       </c>
       <c r="D8">
-        <v>1345.272201293515</v>
+        <v>1352.715170890311</v>
       </c>
       <c r="E8">
-        <v>-51.50929261575658</v>
+        <v>-36.85174694963152</v>
       </c>
       <c r="F8">
-        <v>87.94527399675042</v>
+        <v>102.6028196628755</v>
       </c>
       <c r="G8">
         <v>137.6</v>
@@ -1943,28 +1943,28 @@
         <v>84.63</v>
       </c>
       <c r="M8">
-        <v>4.423647282036546</v>
+        <v>5.160921829042636</v>
       </c>
       <c r="N8">
-        <v>80.20635271796345</v>
+        <v>79.46907817095736</v>
       </c>
       <c r="O8">
-        <v>25.66603286974831</v>
+        <v>25.43010501470636</v>
       </c>
       <c r="P8">
-        <v>54.54031984821515</v>
+        <v>54.038973156251</v>
       </c>
       <c r="Q8">
-        <v>91.44031984821515</v>
+        <v>90.938973156251</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1027004286529399</v>
+        <v>0.1031246192575374</v>
       </c>
       <c r="T8">
-        <v>0.7416033327379682</v>
+        <v>0.7471319583306578</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.13127213909295</v>
+        <v>16.39823326207967</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0983001759095098</v>
+        <v>0.09800970888525611</v>
       </c>
       <c r="C9">
-        <v>1387.712351227436</v>
+        <v>1380.580592598639</v>
       </c>
       <c r="D9">
-        <v>1352.715170890311</v>
+        <v>1360.24095792764</v>
       </c>
       <c r="E9">
-        <v>-36.85174694963149</v>
+        <v>-22.19420128350643</v>
       </c>
       <c r="F9">
-        <v>102.6028196628755</v>
+        <v>117.2603653290006</v>
       </c>
       <c r="G9">
         <v>137.6</v>
@@ -2025,28 +2025,28 @@
         <v>84.63</v>
       </c>
       <c r="M9">
-        <v>5.160921829042637</v>
+        <v>5.898196376048728</v>
       </c>
       <c r="N9">
-        <v>79.46907817095736</v>
+        <v>78.73180362395127</v>
       </c>
       <c r="O9">
-        <v>25.43010501470636</v>
+        <v>25.19417715966441</v>
       </c>
       <c r="P9">
-        <v>54.038973156251</v>
+        <v>53.53762646428686</v>
       </c>
       <c r="Q9">
-        <v>90.938973156251</v>
+        <v>90.43762646428686</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1031246192575374</v>
+        <v>0.1035580313970175</v>
       </c>
       <c r="T9">
-        <v>0.7471319583306578</v>
+        <v>0.7527807714362318</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.39823326207966</v>
+        <v>14.34845410431971</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09800970888525611</v>
+        <v>0.0978110418610024</v>
       </c>
       <c r="C10">
-        <v>1380.580592598639</v>
+        <v>1371.118771027057</v>
       </c>
       <c r="D10">
-        <v>1360.24095792764</v>
+        <v>1365.436682022183</v>
       </c>
       <c r="E10">
-        <v>-22.19420128350643</v>
+        <v>-7.536655617381371</v>
       </c>
       <c r="F10">
-        <v>117.2603653290006</v>
+        <v>131.9179109951256</v>
       </c>
       <c r="G10">
         <v>137.6</v>
@@ -2107,45 +2107,45 @@
         <v>84.63</v>
       </c>
       <c r="M10">
-        <v>5.898196376048728</v>
+        <v>6.833347789547507</v>
       </c>
       <c r="N10">
-        <v>78.73180362395127</v>
+        <v>77.79665221045249</v>
       </c>
       <c r="O10">
-        <v>25.19417715966441</v>
+        <v>24.8949287073448</v>
       </c>
       <c r="P10">
-        <v>53.53762646428686</v>
+        <v>52.90172350310769</v>
       </c>
       <c r="Q10">
-        <v>90.43762646428686</v>
+        <v>89.8017235031077</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1035580313970175</v>
+        <v>0.1040009690780246</v>
       </c>
       <c r="T10">
-        <v>0.7527807714362318</v>
+        <v>0.75855373428039</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.32</v>
       </c>
       <c r="W10">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>14.34845410431971</v>
+        <v>12.3848518480872</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0978110418610024</v>
+        <v>0.09753077483674867</v>
       </c>
       <c r="C11">
-        <v>1371.118771027057</v>
+        <v>1363.858889070492</v>
       </c>
       <c r="D11">
-        <v>1365.436682022183</v>
+        <v>1372.834345731743</v>
       </c>
       <c r="E11">
-        <v>-7.536655617381371</v>
+        <v>7.120890048743689</v>
       </c>
       <c r="F11">
-        <v>131.9179109951256</v>
+        <v>146.5754566612507</v>
       </c>
       <c r="G11">
         <v>137.6</v>
@@ -2189,28 +2189,28 @@
         <v>84.63</v>
       </c>
       <c r="M11">
-        <v>6.833347789547507</v>
+        <v>7.592608655052786</v>
       </c>
       <c r="N11">
-        <v>77.79665221045249</v>
+        <v>77.03739134494721</v>
       </c>
       <c r="O11">
-        <v>24.8949287073448</v>
+        <v>24.65196523038311</v>
       </c>
       <c r="P11">
-        <v>52.90172350310769</v>
+        <v>52.3854261145641</v>
       </c>
       <c r="Q11">
-        <v>89.8017235031077</v>
+        <v>89.2854261145641</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1040009690780246</v>
+        <v>0.1044537498186096</v>
       </c>
       <c r="T11">
-        <v>0.75855373428039</v>
+        <v>0.7644549851877516</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.3848518480872</v>
+        <v>11.14636666327848</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09753077483674867</v>
+        <v>0.09725050781249495</v>
       </c>
       <c r="C12">
-        <v>1363.858889070492</v>
+        <v>1356.679601894522</v>
       </c>
       <c r="D12">
-        <v>1372.834345731743</v>
+        <v>1380.312604221897</v>
       </c>
       <c r="E12">
-        <v>7.120890048743718</v>
+        <v>21.77843571486878</v>
       </c>
       <c r="F12">
-        <v>146.5754566612507</v>
+        <v>161.2330023273758</v>
       </c>
       <c r="G12">
         <v>137.6</v>
@@ -2271,28 +2271,28 @@
         <v>84.63</v>
       </c>
       <c r="M12">
-        <v>7.592608655052786</v>
+        <v>8.351869520558065</v>
       </c>
       <c r="N12">
-        <v>77.03739134494721</v>
+        <v>76.27813047944193</v>
       </c>
       <c r="O12">
-        <v>24.65196523038311</v>
+        <v>24.40900175342142</v>
       </c>
       <c r="P12">
-        <v>52.3854261145641</v>
+        <v>51.86912872602051</v>
       </c>
       <c r="Q12">
-        <v>89.2854261145641</v>
+        <v>88.76912872602051</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1044537498186096</v>
+        <v>0.1049167054072977</v>
       </c>
       <c r="T12">
-        <v>0.7644549851877516</v>
+        <v>0.7704888484750538</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.14636666327847</v>
+        <v>10.13306060298043</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09725050781249495</v>
+        <v>0.09710896078824124</v>
       </c>
       <c r="C13">
-        <v>1356.679601894522</v>
+        <v>1345.829951353652</v>
       </c>
       <c r="D13">
-        <v>1380.312604221897</v>
+        <v>1384.120499347153</v>
       </c>
       <c r="E13">
-        <v>21.77843571486878</v>
+        <v>36.43598138099384</v>
       </c>
       <c r="F13">
-        <v>161.2330023273758</v>
+        <v>175.8905479935008</v>
       </c>
       <c r="G13">
         <v>137.6</v>
@@ -2353,45 +2353,45 @@
         <v>84.63</v>
       </c>
       <c r="M13">
-        <v>8.351869520558065</v>
+        <v>9.410144317652295</v>
       </c>
       <c r="N13">
-        <v>76.27813047944193</v>
+        <v>75.2198556823477</v>
       </c>
       <c r="O13">
-        <v>24.40900175342142</v>
+        <v>24.07035381835126</v>
       </c>
       <c r="P13">
-        <v>51.86912872602051</v>
+        <v>51.14950186399643</v>
       </c>
       <c r="Q13">
-        <v>88.76912872602051</v>
+        <v>88.04950186399643</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1049167054072977</v>
+        <v>0.1053901827139105</v>
       </c>
       <c r="T13">
-        <v>0.7704888484750538</v>
+        <v>0.7766598450188859</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.32</v>
       </c>
       <c r="W13">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.13306060298043</v>
+        <v>8.993485874732478</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09710896078824124</v>
+        <v>0.09684025376398751</v>
       </c>
       <c r="C14">
-        <v>1345.829951353652</v>
+        <v>1338.459260143776</v>
       </c>
       <c r="D14">
-        <v>1384.120499347153</v>
+        <v>1391.407353803402</v>
       </c>
       <c r="E14">
-        <v>36.43598138099384</v>
+        <v>51.09352704711893</v>
       </c>
       <c r="F14">
-        <v>175.8905479935008</v>
+        <v>190.5480936596259</v>
       </c>
       <c r="G14">
         <v>137.6</v>
@@ -2435,28 +2435,28 @@
         <v>84.63</v>
       </c>
       <c r="M14">
-        <v>9.410144317652295</v>
+        <v>10.19432301078999</v>
       </c>
       <c r="N14">
-        <v>75.2198556823477</v>
+        <v>74.43567698921001</v>
       </c>
       <c r="O14">
-        <v>24.07035381835126</v>
+        <v>23.8194166365472</v>
       </c>
       <c r="P14">
-        <v>51.14950186399643</v>
+        <v>50.61626035266281</v>
       </c>
       <c r="Q14">
-        <v>88.04950186399643</v>
+        <v>87.51626035266281</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1053901827139105</v>
+        <v>0.1058745445563075</v>
       </c>
       <c r="T14">
-        <v>0.7766598450188859</v>
+        <v>0.7829727035522311</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.993485874732478</v>
+        <v>8.301679268983825</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09684025376398751</v>
+        <v>0.09657154673973382</v>
       </c>
       <c r="C15">
-        <v>1338.459260143776</v>
+        <v>1331.165699890224</v>
       </c>
       <c r="D15">
-        <v>1391.407353803402</v>
+        <v>1398.771339215975</v>
       </c>
       <c r="E15">
-        <v>51.09352704711893</v>
+        <v>65.75107271324401</v>
       </c>
       <c r="F15">
-        <v>190.5480936596259</v>
+        <v>205.205639325751</v>
       </c>
       <c r="G15">
         <v>137.6</v>
@@ -2517,28 +2517,28 @@
         <v>84.63</v>
       </c>
       <c r="M15">
-        <v>10.19432301078999</v>
+        <v>10.97850170392768</v>
       </c>
       <c r="N15">
-        <v>74.43567698921001</v>
+        <v>73.65149829607232</v>
       </c>
       <c r="O15">
-        <v>23.8194166365472</v>
+        <v>23.56847945474314</v>
       </c>
       <c r="P15">
-        <v>50.61626035266281</v>
+        <v>50.08301884132918</v>
       </c>
       <c r="Q15">
-        <v>87.51626035266281</v>
+        <v>86.98301884132917</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1058745445563075</v>
+        <v>0.1063701706275975</v>
       </c>
       <c r="T15">
-        <v>0.7829727035522311</v>
+        <v>0.7894323727491426</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.301679268983825</v>
+        <v>7.708702178342122</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09657154673973382</v>
+        <v>0.09638443971548011</v>
       </c>
       <c r="C16">
-        <v>1331.165699890224</v>
+        <v>1321.682076172512</v>
       </c>
       <c r="D16">
-        <v>1398.771339215975</v>
+        <v>1403.945261164388</v>
       </c>
       <c r="E16">
-        <v>65.75107271324401</v>
+        <v>80.4086183793691</v>
       </c>
       <c r="F16">
-        <v>205.205639325751</v>
+        <v>219.8631849918761</v>
       </c>
       <c r="G16">
         <v>137.6</v>
@@ -2599,45 +2599,45 @@
         <v>84.63</v>
       </c>
       <c r="M16">
-        <v>10.97850170392768</v>
+        <v>11.93857094505887</v>
       </c>
       <c r="N16">
-        <v>73.65149829607232</v>
+        <v>72.69142905494112</v>
       </c>
       <c r="O16">
-        <v>23.56847945474314</v>
+        <v>23.26125729758116</v>
       </c>
       <c r="P16">
-        <v>50.08301884132918</v>
+        <v>49.43017175735996</v>
       </c>
       <c r="Q16">
-        <v>86.98301884132917</v>
+        <v>86.33017175735996</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1063701706275975</v>
+        <v>0.1068774584888001</v>
       </c>
       <c r="T16">
-        <v>0.7894323727491426</v>
+        <v>0.7960440341624522</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.32</v>
       </c>
       <c r="W16">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.708702178342122</v>
+        <v>7.088788129623387</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09638443971548011</v>
+        <v>0.09612117269122639</v>
       </c>
       <c r="C17">
-        <v>1321.682076172512</v>
+        <v>1314.369599616557</v>
       </c>
       <c r="D17">
-        <v>1403.945261164388</v>
+        <v>1411.290330274558</v>
       </c>
       <c r="E17">
-        <v>80.40861837936905</v>
+        <v>95.06616404549413</v>
       </c>
       <c r="F17">
-        <v>219.863184991876</v>
+        <v>234.5207306580011</v>
       </c>
       <c r="G17">
         <v>137.6</v>
@@ -2681,28 +2681,28 @@
         <v>84.63</v>
       </c>
       <c r="M17">
-        <v>11.93857094505887</v>
+        <v>12.73447567472946</v>
       </c>
       <c r="N17">
-        <v>72.69142905494112</v>
+        <v>71.89552432527053</v>
       </c>
       <c r="O17">
-        <v>23.26125729758116</v>
+        <v>23.00656778408657</v>
       </c>
       <c r="P17">
-        <v>49.43017175735996</v>
+        <v>48.88895654118396</v>
       </c>
       <c r="Q17">
-        <v>86.33017175735996</v>
+        <v>85.78895654118395</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1068774584888001</v>
+        <v>0.1073968246324124</v>
       </c>
       <c r="T17">
-        <v>0.7960440341624522</v>
+        <v>0.8028131160856022</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.088788129623389</v>
+        <v>6.645738871521926</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09612117269122639</v>
+        <v>0.09585790566697266</v>
       </c>
       <c r="C18">
-        <v>1314.369599616557</v>
+        <v>1307.134382165305</v>
       </c>
       <c r="D18">
-        <v>1411.290330274558</v>
+        <v>1418.712658489432</v>
       </c>
       <c r="E18">
-        <v>95.06616404549413</v>
+        <v>109.7237097116192</v>
       </c>
       <c r="F18">
-        <v>234.5207306580011</v>
+        <v>249.1782763241262</v>
       </c>
       <c r="G18">
         <v>137.6</v>
@@ -2763,28 +2763,28 @@
         <v>84.63</v>
       </c>
       <c r="M18">
-        <v>12.73447567472946</v>
+        <v>13.53038040440005</v>
       </c>
       <c r="N18">
-        <v>71.89552432527053</v>
+        <v>71.09961959559995</v>
       </c>
       <c r="O18">
-        <v>23.00656778408657</v>
+        <v>22.75187827059198</v>
       </c>
       <c r="P18">
-        <v>48.88895654118396</v>
+        <v>48.34774132500796</v>
       </c>
       <c r="Q18">
-        <v>85.78895654118395</v>
+        <v>85.24774132500795</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1073968246324124</v>
+        <v>0.1079287056228586</v>
       </c>
       <c r="T18">
-        <v>0.8028131160856022</v>
+        <v>0.809745308416539</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.645738871521926</v>
+        <v>6.254813055550049</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09585790566697266</v>
+        <v>0.09571703864271895</v>
       </c>
       <c r="C19">
-        <v>1307.134382165305</v>
+        <v>1296.480476056064</v>
       </c>
       <c r="D19">
-        <v>1418.712658489432</v>
+        <v>1422.716298046315</v>
       </c>
       <c r="E19">
-        <v>109.7237097116192</v>
+        <v>124.3812553777443</v>
       </c>
       <c r="F19">
-        <v>249.1782763241262</v>
+        <v>263.8358219902513</v>
       </c>
       <c r="G19">
         <v>137.6</v>
@@ -2845,45 +2845,45 @@
         <v>84.63</v>
       </c>
       <c r="M19">
-        <v>13.53038040440005</v>
+        <v>14.5901209560609</v>
       </c>
       <c r="N19">
-        <v>71.09961959559995</v>
+        <v>70.0398790439391</v>
       </c>
       <c r="O19">
-        <v>22.75187827059198</v>
+        <v>22.41276129406051</v>
       </c>
       <c r="P19">
-        <v>48.34774132500796</v>
+        <v>47.62711774987858</v>
       </c>
       <c r="Q19">
-        <v>85.24774132500795</v>
+        <v>84.52711774987858</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1079287056228586</v>
+        <v>0.108473559320389</v>
       </c>
       <c r="T19">
-        <v>0.809745308416539</v>
+        <v>0.816846578609206</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.32</v>
       </c>
       <c r="W19">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.254813055550049</v>
+        <v>5.800500232648432</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09571703864271897</v>
+        <v>0.09546057161846525</v>
       </c>
       <c r="C20">
-        <v>1296.480476056064</v>
+        <v>1289.170405528173</v>
       </c>
       <c r="D20">
-        <v>1422.716298046315</v>
+        <v>1430.06377318455</v>
       </c>
       <c r="E20">
-        <v>124.3812553777443</v>
+        <v>139.0388010438693</v>
       </c>
       <c r="F20">
-        <v>263.8358219902512</v>
+        <v>278.4933676563763</v>
       </c>
       <c r="G20">
         <v>137.6</v>
@@ -2927,28 +2927,28 @@
         <v>84.63</v>
       </c>
       <c r="M20">
-        <v>14.5901209560609</v>
+        <v>15.40068323139761</v>
       </c>
       <c r="N20">
-        <v>70.0398790439391</v>
+        <v>69.22931676860239</v>
       </c>
       <c r="O20">
-        <v>22.41276129406051</v>
+        <v>22.15338136595276</v>
       </c>
       <c r="P20">
-        <v>47.62711774987858</v>
+        <v>47.07593540264962</v>
       </c>
       <c r="Q20">
-        <v>84.52711774987858</v>
+        <v>83.97593540264961</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.108473559320389</v>
+        <v>0.1090318661956361</v>
       </c>
       <c r="T20">
-        <v>0.816846578609206</v>
+        <v>0.8241231888066303</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.800500232648433</v>
+        <v>5.495210746719568</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09546057161846525</v>
+        <v>0.09520410459421152</v>
       </c>
       <c r="C21">
-        <v>1289.170405528173</v>
+        <v>1281.936619555988</v>
       </c>
       <c r="D21">
-        <v>1430.06377318455</v>
+        <v>1437.487532878489</v>
       </c>
       <c r="E21">
-        <v>139.0388010438693</v>
+        <v>153.6963467099944</v>
       </c>
       <c r="F21">
-        <v>278.4933676563763</v>
+        <v>293.1509133225014</v>
       </c>
       <c r="G21">
         <v>137.6</v>
@@ -3009,28 +3009,28 @@
         <v>84.63</v>
       </c>
       <c r="M21">
-        <v>15.40068323139761</v>
+        <v>16.21124550673433</v>
       </c>
       <c r="N21">
-        <v>69.22931676860239</v>
+        <v>68.41875449326567</v>
       </c>
       <c r="O21">
-        <v>22.15338136595276</v>
+        <v>21.89400143784501</v>
       </c>
       <c r="P21">
-        <v>47.07593540264962</v>
+        <v>46.52475305542065</v>
       </c>
       <c r="Q21">
-        <v>83.97593540264961</v>
+        <v>83.42475305542065</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1090318661956361</v>
+        <v>0.1096041307427644</v>
       </c>
       <c r="T21">
-        <v>0.8241231888066303</v>
+        <v>0.8315817142589901</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.495210746719568</v>
+        <v>5.220450209383589</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09520410459421152</v>
+        <v>0.0949476375699578</v>
       </c>
       <c r="C22">
-        <v>1281.936619555988</v>
+        <v>1274.780312366166</v>
       </c>
       <c r="D22">
-        <v>1437.487532878489</v>
+        <v>1444.988771354793</v>
       </c>
       <c r="E22">
-        <v>153.6963467099944</v>
+        <v>168.3538923761195</v>
       </c>
       <c r="F22">
-        <v>293.1509133225014</v>
+        <v>307.8084589886265</v>
       </c>
       <c r="G22">
         <v>137.6</v>
@@ -3091,28 +3091,28 @@
         <v>84.63</v>
       </c>
       <c r="M22">
-        <v>16.21124550673433</v>
+        <v>17.02180778207105</v>
       </c>
       <c r="N22">
-        <v>68.41875449326567</v>
+        <v>67.60819221792894</v>
       </c>
       <c r="O22">
-        <v>21.89400143784501</v>
+        <v>21.63462150973726</v>
       </c>
       <c r="P22">
-        <v>46.52475305542065</v>
+        <v>45.97357070819169</v>
       </c>
       <c r="Q22">
-        <v>83.42475305542065</v>
+        <v>82.87357070819169</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1096041307427644</v>
+        <v>0.1101908829999466</v>
       </c>
       <c r="T22">
-        <v>0.8315817142589901</v>
+        <v>0.8392290631405236</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.220450209383589</v>
+        <v>4.971857342270084</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0949476375699578</v>
+        <v>0.0946911705457041</v>
       </c>
       <c r="C23">
-        <v>1274.780312366166</v>
+        <v>1267.702703243449</v>
       </c>
       <c r="D23">
-        <v>1444.988771354793</v>
+        <v>1452.568707898201</v>
       </c>
       <c r="E23">
-        <v>168.3538923761195</v>
+        <v>183.0114380422445</v>
       </c>
       <c r="F23">
-        <v>307.8084589886265</v>
+        <v>322.4660046547515</v>
       </c>
       <c r="G23">
         <v>137.6</v>
@@ -3173,28 +3173,28 @@
         <v>84.63</v>
       </c>
       <c r="M23">
-        <v>17.02180778207104</v>
+        <v>17.83237005740776</v>
       </c>
       <c r="N23">
-        <v>67.60819221792894</v>
+        <v>66.79762994259224</v>
       </c>
       <c r="O23">
-        <v>21.63462150973726</v>
+        <v>21.37524158162952</v>
       </c>
       <c r="P23">
-        <v>45.97357070819169</v>
+        <v>45.42238836096272</v>
       </c>
       <c r="Q23">
-        <v>82.87357070819169</v>
+        <v>82.32238836096272</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1101908829999466</v>
+        <v>0.1107926801868001</v>
       </c>
       <c r="T23">
-        <v>0.8392290631405236</v>
+        <v>0.8470724978908144</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.971857342270085</v>
+        <v>4.745863826712354</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0946911705457041</v>
+        <v>0.09443470352145038</v>
       </c>
       <c r="C24">
-        <v>1267.702703243449</v>
+        <v>1260.705037191362</v>
       </c>
       <c r="D24">
-        <v>1452.568707898201</v>
+        <v>1460.228587512238</v>
       </c>
       <c r="E24">
-        <v>183.0114380422445</v>
+        <v>197.6689837083696</v>
       </c>
       <c r="F24">
-        <v>322.4660046547515</v>
+        <v>337.1235503208766</v>
       </c>
       <c r="G24">
         <v>137.6</v>
@@ -3255,28 +3255,28 @@
         <v>84.63</v>
       </c>
       <c r="M24">
-        <v>17.83237005740776</v>
+        <v>18.64293233274448</v>
       </c>
       <c r="N24">
-        <v>66.79762994259224</v>
+        <v>65.98706766725552</v>
       </c>
       <c r="O24">
-        <v>21.37524158162952</v>
+        <v>21.11586165352177</v>
       </c>
       <c r="P24">
-        <v>45.42238836096272</v>
+        <v>44.87120601373375</v>
       </c>
       <c r="Q24">
-        <v>82.32238836096272</v>
+        <v>81.77120601373375</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1107926801868001</v>
+        <v>0.1114101084694161</v>
       </c>
       <c r="T24">
-        <v>0.8470724978908144</v>
+        <v>0.8551196582190347</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.745863826712354</v>
+        <v>4.539521921203121</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09443470352145038</v>
+        <v>0.09458623649719668</v>
       </c>
       <c r="C25">
-        <v>1260.705037191362</v>
+        <v>1241.511933978217</v>
       </c>
       <c r="D25">
-        <v>1460.228587512238</v>
+        <v>1455.693029965219</v>
       </c>
       <c r="E25">
-        <v>197.6689837083696</v>
+        <v>212.3265293744947</v>
       </c>
       <c r="F25">
-        <v>337.1235503208766</v>
+        <v>351.7810959870017</v>
       </c>
       <c r="G25">
         <v>137.6</v>
@@ -3337,45 +3337,45 @@
         <v>84.63</v>
       </c>
       <c r="M25">
-        <v>18.64293233274448</v>
+        <v>20.3329473480487</v>
       </c>
       <c r="N25">
-        <v>65.98706766725552</v>
+        <v>64.29705265195129</v>
       </c>
       <c r="O25">
-        <v>21.11586165352177</v>
+        <v>20.57505684862441</v>
       </c>
       <c r="P25">
-        <v>44.87120601373375</v>
+        <v>43.72199580332688</v>
       </c>
       <c r="Q25">
-        <v>81.77120601373375</v>
+        <v>80.62199580332688</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1114101084694161</v>
+        <v>0.1120437848647325</v>
       </c>
       <c r="T25">
-        <v>0.8551196582190347</v>
+        <v>0.8633785859243136</v>
       </c>
       <c r="U25">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.32</v>
       </c>
       <c r="W25">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.539521921203121</v>
+        <v>4.162210158288818</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09458623649719668</v>
+        <v>0.09494176947294296</v>
       </c>
       <c r="C26">
-        <v>1241.511933978217</v>
+        <v>1216.322678113874</v>
       </c>
       <c r="D26">
-        <v>1455.693029965219</v>
+        <v>1445.161319767001</v>
       </c>
       <c r="E26">
-        <v>212.3265293744947</v>
+        <v>226.9840750406198</v>
       </c>
       <c r="F26">
-        <v>351.7810959870017</v>
+        <v>366.4386416531268</v>
       </c>
       <c r="G26">
         <v>137.6</v>
@@ -3419,45 +3419,45 @@
         <v>84.63</v>
       </c>
       <c r="M26">
-        <v>20.3329473480487</v>
+        <v>22.46268873333667</v>
       </c>
       <c r="N26">
-        <v>64.2970526519513</v>
+        <v>62.16731126666333</v>
       </c>
       <c r="O26">
-        <v>20.57505684862442</v>
+        <v>19.89353960533226</v>
       </c>
       <c r="P26">
-        <v>43.72199580332689</v>
+        <v>42.27377166133106</v>
       </c>
       <c r="Q26">
-        <v>80.62199580332688</v>
+        <v>79.17377166133106</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1120437848647325</v>
+        <v>0.1126943592972573</v>
       </c>
       <c r="T26">
-        <v>0.8633785859243136</v>
+        <v>0.8718577517017332</v>
       </c>
       <c r="U26">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V26">
         <v>0.32</v>
       </c>
       <c r="W26">
-        <v>0.039304</v>
+        <v>0.041684</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.162210158288819</v>
+        <v>3.767581032024959</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09494176947294296</v>
+        <v>0.09472610244868923</v>
       </c>
       <c r="C27">
-        <v>1216.322678113874</v>
+        <v>1208.035426131526</v>
       </c>
       <c r="D27">
-        <v>1445.161319767001</v>
+        <v>1451.531613450778</v>
       </c>
       <c r="E27">
-        <v>226.9840750406198</v>
+        <v>241.6416207067448</v>
       </c>
       <c r="F27">
-        <v>366.4386416531268</v>
+        <v>381.0961873192518</v>
       </c>
       <c r="G27">
         <v>137.6</v>
@@ -3501,28 +3501,28 @@
         <v>84.63</v>
       </c>
       <c r="M27">
-        <v>22.46268873333667</v>
+        <v>23.36119628267014</v>
       </c>
       <c r="N27">
-        <v>62.16731126666333</v>
+        <v>61.26880371732986</v>
       </c>
       <c r="O27">
-        <v>19.89353960533226</v>
+        <v>19.60601718954555</v>
       </c>
       <c r="P27">
-        <v>42.27377166133106</v>
+        <v>41.66278652778431</v>
       </c>
       <c r="Q27">
-        <v>79.17377166133106</v>
+        <v>78.56278652778431</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1126943592972573</v>
+        <v>0.113362516822553</v>
       </c>
       <c r="T27">
-        <v>0.8718577517017332</v>
+        <v>0.8805660841217857</v>
       </c>
       <c r="U27">
         <v>0.0613</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.767581032024959</v>
+        <v>3.622674069254768</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09472610244868923</v>
+        <v>0.09502451542443553</v>
       </c>
       <c r="C28">
-        <v>1208.035426131526</v>
+        <v>1184.578284076797</v>
       </c>
       <c r="D28">
-        <v>1451.531613450778</v>
+        <v>1442.732017062174</v>
       </c>
       <c r="E28">
-        <v>241.6416207067448</v>
+        <v>256.2991663728699</v>
       </c>
       <c r="F28">
-        <v>381.0961873192518</v>
+        <v>395.7537329853769</v>
       </c>
       <c r="G28">
         <v>137.6</v>
@@ -3583,45 +3583,45 @@
         <v>84.63</v>
       </c>
       <c r="M28">
-        <v>23.36119628267014</v>
+        <v>25.36781428436266</v>
       </c>
       <c r="N28">
-        <v>61.26880371732986</v>
+        <v>59.26218571563733</v>
       </c>
       <c r="O28">
-        <v>19.60601718954555</v>
+        <v>18.96389942900394</v>
       </c>
       <c r="P28">
-        <v>41.66278652778431</v>
+        <v>40.29828628663338</v>
       </c>
       <c r="Q28">
-        <v>78.56278652778431</v>
+        <v>77.19828628663339</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.113362516822553</v>
+        <v>0.1140489800334733</v>
       </c>
       <c r="T28">
-        <v>0.8805660841217857</v>
+        <v>0.8895130009917028</v>
       </c>
       <c r="U28">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V28">
         <v>0.32</v>
       </c>
       <c r="W28">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.622674069254768</v>
+        <v>3.336117138486306</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09502451542443553</v>
+        <v>0.09482788840018182</v>
       </c>
       <c r="C29">
-        <v>1184.578284076797</v>
+        <v>1175.706835111288</v>
       </c>
       <c r="D29">
-        <v>1442.732017062174</v>
+        <v>1448.518113762791</v>
       </c>
       <c r="E29">
-        <v>256.2991663728699</v>
+        <v>270.956712038995</v>
       </c>
       <c r="F29">
-        <v>395.7537329853769</v>
+        <v>410.411278651502</v>
       </c>
       <c r="G29">
         <v>137.6</v>
@@ -3665,28 +3665,28 @@
         <v>84.63</v>
       </c>
       <c r="M29">
-        <v>25.36781428436266</v>
+        <v>26.30736296156128</v>
       </c>
       <c r="N29">
-        <v>59.26218571563733</v>
+        <v>58.32263703843871</v>
       </c>
       <c r="O29">
-        <v>18.96389942900394</v>
+        <v>18.66324385230039</v>
       </c>
       <c r="P29">
-        <v>40.29828628663338</v>
+        <v>39.65939318613832</v>
       </c>
       <c r="Q29">
-        <v>77.19828628663339</v>
+        <v>76.55939318613832</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1140489800334733</v>
+        <v>0.1147545116669192</v>
       </c>
       <c r="T29">
-        <v>0.8895130009917028</v>
+        <v>0.8987084433302286</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.336117138486306</v>
+        <v>3.21697009782608</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09482788840018182</v>
+        <v>0.09463126137592807</v>
       </c>
       <c r="C30">
-        <v>1175.706835111288</v>
+        <v>1166.881983466605</v>
       </c>
       <c r="D30">
-        <v>1448.518113762791</v>
+        <v>1454.350807784232</v>
       </c>
       <c r="E30">
-        <v>270.956712038995</v>
+        <v>285.6142577051201</v>
       </c>
       <c r="F30">
-        <v>410.411278651502</v>
+        <v>425.0688243176271</v>
       </c>
       <c r="G30">
         <v>137.6</v>
@@ -3747,28 +3747,28 @@
         <v>84.63</v>
       </c>
       <c r="M30">
-        <v>26.30736296156128</v>
+        <v>27.2469116387599</v>
       </c>
       <c r="N30">
-        <v>58.32263703843871</v>
+        <v>57.3830883612401</v>
       </c>
       <c r="O30">
-        <v>18.66324385230039</v>
+        <v>18.36258827559683</v>
       </c>
       <c r="P30">
-        <v>39.65939318613832</v>
+        <v>39.02050008564326</v>
       </c>
       <c r="Q30">
-        <v>76.55939318613832</v>
+        <v>75.92050008564325</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1147545116669192</v>
+        <v>0.1154799174308846</v>
       </c>
       <c r="T30">
-        <v>0.8987084433302286</v>
+        <v>0.9081629122135015</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.21697009782608</v>
+        <v>3.106040094452767</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09463126137592807</v>
+        <v>0.09443463435167437</v>
       </c>
       <c r="C31">
-        <v>1166.881983466605</v>
+        <v>1158.104294313594</v>
       </c>
       <c r="D31">
-        <v>1454.350807784232</v>
+        <v>1460.230664297346</v>
       </c>
       <c r="E31">
-        <v>285.61425770512</v>
+        <v>300.2718033712451</v>
       </c>
       <c r="F31">
-        <v>425.068824317627</v>
+        <v>439.7263699837521</v>
       </c>
       <c r="G31">
         <v>137.6</v>
@@ -3829,28 +3829,28 @@
         <v>84.63</v>
       </c>
       <c r="M31">
-        <v>27.24691163875989</v>
+        <v>28.18646031595851</v>
       </c>
       <c r="N31">
-        <v>57.38308836124011</v>
+        <v>56.44353968404148</v>
       </c>
       <c r="O31">
-        <v>18.36258827559683</v>
+        <v>18.06193269889328</v>
       </c>
       <c r="P31">
-        <v>39.02050008564327</v>
+        <v>38.38160698514821</v>
       </c>
       <c r="Q31">
-        <v>75.92050008564327</v>
+        <v>75.28160698514822</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1154799174308846</v>
+        <v>0.1162260490738205</v>
       </c>
       <c r="T31">
-        <v>0.9081629122135015</v>
+        <v>0.9178875087791538</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.106040094452768</v>
+        <v>3.002505424637675</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09443463435167437</v>
+        <v>0.09588224732742065</v>
       </c>
       <c r="C32">
-        <v>1158.104294313594</v>
+        <v>1101.239200663453</v>
       </c>
       <c r="D32">
-        <v>1460.230664297346</v>
+        <v>1418.02311631333</v>
       </c>
       <c r="E32">
-        <v>300.2718033712451</v>
+        <v>314.9293490373702</v>
       </c>
       <c r="F32">
-        <v>439.7263699837521</v>
+        <v>454.3839156498772</v>
       </c>
       <c r="G32">
         <v>137.6</v>
@@ -3911,45 +3911,45 @@
         <v>84.63</v>
       </c>
       <c r="M32">
-        <v>28.18646031595851</v>
+        <v>32.67020353522617</v>
       </c>
       <c r="N32">
-        <v>56.44353968404148</v>
+        <v>51.95979646477382</v>
       </c>
       <c r="O32">
-        <v>18.06193269889328</v>
+        <v>16.62713486872762</v>
       </c>
       <c r="P32">
-        <v>38.38160698514821</v>
+        <v>35.3326615960462</v>
       </c>
       <c r="Q32">
-        <v>75.28160698514822</v>
+        <v>72.2326615960462</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1162260490738205</v>
+        <v>0.1169938077208995</v>
       </c>
       <c r="T32">
-        <v>0.9178875087791538</v>
+        <v>0.9278939777090279</v>
       </c>
       <c r="U32">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V32">
         <v>0.32</v>
       </c>
       <c r="W32">
-        <v>0.043588</v>
+        <v>0.048892</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.002505424637675</v>
+        <v>2.590433815594351</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09588224732742065</v>
+        <v>0.09573866030316695</v>
       </c>
       <c r="C33">
-        <v>1101.239200663453</v>
+        <v>1090.65885126888</v>
       </c>
       <c r="D33">
-        <v>1418.02311631333</v>
+        <v>1422.100312584882</v>
       </c>
       <c r="E33">
-        <v>314.9293490373702</v>
+        <v>329.5868947034953</v>
       </c>
       <c r="F33">
-        <v>454.3839156498772</v>
+        <v>469.0414613160023</v>
       </c>
       <c r="G33">
         <v>137.6</v>
@@ -3993,28 +3993,28 @@
         <v>84.63</v>
       </c>
       <c r="M33">
-        <v>32.67020353522617</v>
+        <v>33.72408106862056</v>
       </c>
       <c r="N33">
-        <v>51.95979646477382</v>
+        <v>50.90591893137943</v>
       </c>
       <c r="O33">
-        <v>16.62713486872762</v>
+        <v>16.28989405804142</v>
       </c>
       <c r="P33">
-        <v>35.3326615960462</v>
+        <v>34.61602487333801</v>
       </c>
       <c r="Q33">
-        <v>72.2326615960462</v>
+        <v>71.51602487333801</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1169938077208995</v>
+        <v>0.1177841475046573</v>
       </c>
       <c r="T33">
-        <v>0.9278939777090279</v>
+        <v>0.9381947545486042</v>
       </c>
       <c r="U33">
         <v>0.07190000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.590433815594351</v>
+        <v>2.509482758857028</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09573866030316695</v>
+        <v>0.09647023327891324</v>
       </c>
       <c r="C34">
-        <v>1090.65885126888</v>
+        <v>1055.469129408484</v>
       </c>
       <c r="D34">
-        <v>1422.100312584882</v>
+        <v>1401.568136390611</v>
       </c>
       <c r="E34">
-        <v>329.5868947034953</v>
+        <v>344.2444403696203</v>
       </c>
       <c r="F34">
-        <v>469.0414613160023</v>
+        <v>483.6990069821273</v>
       </c>
       <c r="G34">
         <v>137.6</v>
@@ -4075,45 +4075,45 @@
         <v>84.63</v>
       </c>
       <c r="M34">
-        <v>33.72408106862056</v>
+        <v>36.66438472924526</v>
       </c>
       <c r="N34">
-        <v>50.90591893137943</v>
+        <v>47.96561527075474</v>
       </c>
       <c r="O34">
-        <v>16.28989405804142</v>
+        <v>15.34899688664152</v>
       </c>
       <c r="P34">
-        <v>34.61602487333801</v>
+        <v>32.61661838411322</v>
       </c>
       <c r="Q34">
-        <v>71.51602487333801</v>
+        <v>69.51661838411323</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1177841475046573</v>
+        <v>0.118598079520766</v>
       </c>
       <c r="T34">
-        <v>0.9381947545486042</v>
+        <v>0.9488030172639887</v>
       </c>
       <c r="U34">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V34">
         <v>0.32</v>
       </c>
       <c r="W34">
-        <v>0.048892</v>
+        <v>0.051544</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.509482758857028</v>
+        <v>2.308234561276985</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09647023327891324</v>
+        <v>0.09635316625465952</v>
       </c>
       <c r="C35">
-        <v>1055.469129408484</v>
+        <v>1044.057224385114</v>
       </c>
       <c r="D35">
-        <v>1401.568136390611</v>
+        <v>1404.813777033366</v>
       </c>
       <c r="E35">
-        <v>344.2444403696203</v>
+        <v>358.9019860357454</v>
       </c>
       <c r="F35">
-        <v>483.6990069821273</v>
+        <v>498.3565526482524</v>
       </c>
       <c r="G35">
         <v>137.6</v>
@@ -4157,28 +4157,28 @@
         <v>84.63</v>
       </c>
       <c r="M35">
-        <v>36.66438472924526</v>
+        <v>37.77542669073754</v>
       </c>
       <c r="N35">
-        <v>47.96561527075474</v>
+        <v>46.85457330926246</v>
       </c>
       <c r="O35">
-        <v>15.34899688664152</v>
+        <v>14.99346345896399</v>
       </c>
       <c r="P35">
-        <v>32.61661838411322</v>
+        <v>31.86110985029847</v>
       </c>
       <c r="Q35">
-        <v>69.51661838411323</v>
+        <v>68.76110985029847</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.118598079520766</v>
+        <v>0.1194366761434235</v>
       </c>
       <c r="T35">
-        <v>0.9488030172639887</v>
+        <v>0.9597327424859</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.308234561276985</v>
+        <v>2.24034530947472</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09635316625465952</v>
+        <v>0.0962360992304058</v>
       </c>
       <c r="C36">
-        <v>1044.057224385114</v>
+        <v>1032.660386248266</v>
       </c>
       <c r="D36">
-        <v>1404.813777033366</v>
+        <v>1408.074484562643</v>
       </c>
       <c r="E36">
-        <v>358.9019860357454</v>
+        <v>373.5595317018705</v>
       </c>
       <c r="F36">
-        <v>498.3565526482524</v>
+        <v>513.0140983143775</v>
       </c>
       <c r="G36">
         <v>137.6</v>
@@ -4239,28 +4239,28 @@
         <v>84.63</v>
       </c>
       <c r="M36">
-        <v>37.77542669073754</v>
+        <v>38.88646865222982</v>
       </c>
       <c r="N36">
-        <v>46.85457330926246</v>
+        <v>45.74353134777018</v>
       </c>
       <c r="O36">
-        <v>14.99346345896399</v>
+        <v>14.63793003128646</v>
       </c>
       <c r="P36">
-        <v>31.86110985029847</v>
+        <v>31.10560131648372</v>
       </c>
       <c r="Q36">
-        <v>68.76110985029847</v>
+        <v>68.00560131648372</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1194366761434235</v>
+        <v>0.1203010757390859</v>
       </c>
       <c r="T36">
-        <v>0.9597327424859</v>
+        <v>0.9709987669454087</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.24034530947472</v>
+        <v>2.176335443489728</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0962360992304058</v>
+        <v>0.09611903220615209</v>
       </c>
       <c r="C37">
-        <v>1032.660386248266</v>
+        <v>1021.278720157089</v>
       </c>
       <c r="D37">
-        <v>1408.074484562643</v>
+        <v>1411.350364137592</v>
       </c>
       <c r="E37">
-        <v>373.5595317018705</v>
+        <v>388.2170773679956</v>
       </c>
       <c r="F37">
-        <v>513.0140983143775</v>
+        <v>527.6716439805026</v>
       </c>
       <c r="G37">
         <v>137.6</v>
@@ -4321,28 +4321,28 @@
         <v>84.63</v>
       </c>
       <c r="M37">
-        <v>38.88646865222982</v>
+        <v>39.9975106137221</v>
       </c>
       <c r="N37">
-        <v>45.74353134777018</v>
+        <v>44.6324893862779</v>
       </c>
       <c r="O37">
-        <v>14.63793003128646</v>
+        <v>14.28239660360893</v>
       </c>
       <c r="P37">
-        <v>31.10560131648372</v>
+        <v>30.35009278266897</v>
       </c>
       <c r="Q37">
-        <v>68.00560131648372</v>
+        <v>67.25009278266897</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1203010757390859</v>
+        <v>0.1211924878221126</v>
       </c>
       <c r="T37">
-        <v>0.9709987669454087</v>
+        <v>0.9826168546692768</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.176335443489728</v>
+        <v>2.115881681170569</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0961190322061521</v>
+        <v>0.09600196518189838</v>
       </c>
       <c r="C38">
-        <v>1021.278720157089</v>
+        <v>1009.912332251628</v>
       </c>
       <c r="D38">
-        <v>1411.350364137592</v>
+        <v>1414.641521898256</v>
       </c>
       <c r="E38">
-        <v>388.2170773679955</v>
+        <v>402.8746230341206</v>
       </c>
       <c r="F38">
-        <v>527.6716439805025</v>
+        <v>542.3291896466276</v>
       </c>
       <c r="G38">
         <v>137.6</v>
@@ -4403,28 +4403,28 @@
         <v>84.63</v>
       </c>
       <c r="M38">
-        <v>39.99751061372209</v>
+        <v>41.10855257521438</v>
       </c>
       <c r="N38">
-        <v>44.6324893862779</v>
+        <v>43.52144742478562</v>
       </c>
       <c r="O38">
-        <v>14.28239660360893</v>
+        <v>13.9268631759314</v>
       </c>
       <c r="P38">
-        <v>30.35009278266897</v>
+        <v>29.59458424885422</v>
       </c>
       <c r="Q38">
-        <v>67.25009278266897</v>
+        <v>66.49458424885422</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1211924878221126</v>
+        <v>0.122112198701426</v>
       </c>
       <c r="T38">
-        <v>0.9826168546692766</v>
+        <v>0.9946037705748551</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.11588168117057</v>
+        <v>2.058695689787581</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09600196518189838</v>
+        <v>0.09588489815764466</v>
       </c>
       <c r="C39">
-        <v>1009.912332251628</v>
+        <v>998.5613296642794</v>
       </c>
       <c r="D39">
-        <v>1414.641521898256</v>
+        <v>1417.948064977032</v>
       </c>
       <c r="E39">
-        <v>402.8746230341206</v>
+        <v>417.5321687002457</v>
       </c>
       <c r="F39">
-        <v>542.3291896466276</v>
+        <v>556.9867353127527</v>
       </c>
       <c r="G39">
         <v>137.6</v>
@@ -4485,28 +4485,28 @@
         <v>84.63</v>
       </c>
       <c r="M39">
-        <v>41.10855257521438</v>
+        <v>42.21959453670666</v>
       </c>
       <c r="N39">
-        <v>43.52144742478562</v>
+        <v>42.41040546329334</v>
       </c>
       <c r="O39">
-        <v>13.9268631759314</v>
+        <v>13.57132974825387</v>
       </c>
       <c r="P39">
-        <v>29.59458424885422</v>
+        <v>28.83907571503947</v>
       </c>
       <c r="Q39">
-        <v>66.49458424885422</v>
+        <v>65.73907571503946</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.122112198701426</v>
+        <v>0.1230615776736204</v>
       </c>
       <c r="T39">
-        <v>0.9946037705748551</v>
+        <v>1.006977361187065</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.058695689787581</v>
+        <v>2.00451948742475</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09588489815764466</v>
+        <v>0.09953367113339096</v>
       </c>
       <c r="C40">
-        <v>998.5613296642794</v>
+        <v>887.6183363194291</v>
       </c>
       <c r="D40">
-        <v>1417.948064977032</v>
+        <v>1321.662617298307</v>
       </c>
       <c r="E40">
-        <v>417.5321687002457</v>
+        <v>432.1897143663708</v>
       </c>
       <c r="F40">
-        <v>556.9867353127527</v>
+        <v>571.6442809788778</v>
       </c>
       <c r="G40">
         <v>137.6</v>
@@ -4567,45 +4567,45 @@
         <v>84.63</v>
       </c>
       <c r="M40">
-        <v>42.21959453670666</v>
+        <v>51.447985288099</v>
       </c>
       <c r="N40">
-        <v>42.41040546329334</v>
+        <v>33.182014711901</v>
       </c>
       <c r="O40">
-        <v>13.57132974825387</v>
+        <v>10.61824470780832</v>
       </c>
       <c r="P40">
-        <v>28.83907571503947</v>
+        <v>22.56377000409268</v>
       </c>
       <c r="Q40">
-        <v>65.73907571503946</v>
+        <v>59.46377000409268</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1230615776736204</v>
+        <v>0.1240420838252311</v>
       </c>
       <c r="T40">
-        <v>1.006977361187065</v>
+        <v>1.019756643294757</v>
       </c>
       <c r="U40">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V40">
         <v>0.32</v>
       </c>
       <c r="W40">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.00451948742475</v>
+        <v>1.644962373669017</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09953367113339096</v>
+        <v>0.09951316410913723</v>
       </c>
       <c r="C41">
-        <v>887.6183363194291</v>
+        <v>873.4653851563035</v>
       </c>
       <c r="D41">
-        <v>1321.662617298307</v>
+        <v>1322.167211801306</v>
       </c>
       <c r="E41">
-        <v>432.1897143663708</v>
+        <v>446.8472600324959</v>
       </c>
       <c r="F41">
-        <v>571.6442809788778</v>
+        <v>586.3018266450028</v>
       </c>
       <c r="G41">
         <v>137.6</v>
@@ -4649,28 +4649,28 @@
         <v>84.63</v>
       </c>
       <c r="M41">
-        <v>51.447985288099</v>
+        <v>52.76716439805026</v>
       </c>
       <c r="N41">
-        <v>33.182014711901</v>
+        <v>31.86283560194974</v>
       </c>
       <c r="O41">
-        <v>10.61824470780832</v>
+        <v>10.19610739262392</v>
       </c>
       <c r="P41">
-        <v>22.56377000409268</v>
+        <v>21.66672820932583</v>
       </c>
       <c r="Q41">
-        <v>59.46377000409268</v>
+        <v>58.56672820932582</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1240420838252311</v>
+        <v>0.1250552735152287</v>
       </c>
       <c r="T41">
-        <v>1.019756643294757</v>
+        <v>1.032961901472706</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.644962373669017</v>
+        <v>1.603838314327292</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09951316410913723</v>
+        <v>0.09949265708488352</v>
       </c>
       <c r="C42">
-        <v>873.4653851563035</v>
+        <v>859.312819436263</v>
       </c>
       <c r="D42">
-        <v>1322.167211801306</v>
+        <v>1322.672191747391</v>
       </c>
       <c r="E42">
-        <v>446.8472600324959</v>
+        <v>461.5048056986209</v>
       </c>
       <c r="F42">
-        <v>586.3018266450028</v>
+        <v>600.9593723111279</v>
       </c>
       <c r="G42">
         <v>137.6</v>
@@ -4731,28 +4731,28 @@
         <v>84.63</v>
       </c>
       <c r="M42">
-        <v>52.76716439805026</v>
+        <v>54.08634350800151</v>
       </c>
       <c r="N42">
-        <v>31.86283560194974</v>
+        <v>30.54365649199848</v>
       </c>
       <c r="O42">
-        <v>10.19610739262392</v>
+        <v>9.773970077439515</v>
       </c>
       <c r="P42">
-        <v>21.66672820932583</v>
+        <v>20.76968641455897</v>
       </c>
       <c r="Q42">
-        <v>58.56672820932582</v>
+        <v>57.66968641455897</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1250552735152287</v>
+        <v>0.1261028086184466</v>
       </c>
       <c r="T42">
-        <v>1.032961901472706</v>
+        <v>1.046614795521093</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.603838314327292</v>
+        <v>1.564720306660772</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09949265708488352</v>
+        <v>0.09947215006062979</v>
       </c>
       <c r="C43">
-        <v>859.312819436263</v>
+        <v>845.1606396011184</v>
       </c>
       <c r="D43">
-        <v>1322.672191747391</v>
+        <v>1323.177557578372</v>
       </c>
       <c r="E43">
-        <v>461.5048056986209</v>
+        <v>476.162351364746</v>
       </c>
       <c r="F43">
-        <v>600.9593723111279</v>
+        <v>615.616917977253</v>
       </c>
       <c r="G43">
         <v>137.6</v>
@@ -4813,28 +4813,28 @@
         <v>84.63</v>
       </c>
       <c r="M43">
-        <v>54.08634350800151</v>
+        <v>55.40552261795277</v>
       </c>
       <c r="N43">
-        <v>30.54365649199848</v>
+        <v>29.22447738204723</v>
       </c>
       <c r="O43">
-        <v>9.773970077439515</v>
+        <v>9.351832762255112</v>
       </c>
       <c r="P43">
-        <v>20.76968641455897</v>
+        <v>19.87264461979211</v>
       </c>
       <c r="Q43">
-        <v>57.66968641455897</v>
+        <v>56.77264461979211</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1261028086184466</v>
+        <v>0.1271864656217755</v>
       </c>
       <c r="T43">
-        <v>1.046614795521093</v>
+        <v>1.060738479019425</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.564720306660772</v>
+        <v>1.527465061264087</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0994721500606298</v>
+        <v>0.1184236596749217</v>
       </c>
       <c r="C44">
-        <v>845.1606396011181</v>
+        <v>485.21324877836</v>
       </c>
       <c r="D44">
-        <v>1323.177557578371</v>
+        <v>977.8877124217381</v>
       </c>
       <c r="E44">
-        <v>476.1623513647459</v>
+        <v>490.819897030871</v>
       </c>
       <c r="F44">
-        <v>615.6169179772529</v>
+        <v>630.274463643378</v>
       </c>
       <c r="G44">
         <v>137.6</v>
@@ -4895,45 +4895,45 @@
         <v>84.63</v>
       </c>
       <c r="M44">
-        <v>55.40552261795276</v>
+        <v>92.5242912628479</v>
       </c>
       <c r="N44">
-        <v>29.22447738204723</v>
+        <v>-7.894291262847901</v>
       </c>
       <c r="O44">
-        <v>9.351832762255114</v>
+        <v>-2.526173204111328</v>
       </c>
       <c r="P44">
-        <v>19.87264461979212</v>
+        <v>-5.368118058736572</v>
       </c>
       <c r="Q44">
-        <v>56.77264461979212</v>
+        <v>31.53188194126343</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1271864656217755</v>
+        <v>0.1294313632560913</v>
       </c>
       <c r="T44">
-        <v>1.060738479019425</v>
+        <v>1.089997020768182</v>
       </c>
       <c r="U44">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.32</v>
+        <v>0.2926971893582536</v>
       </c>
       <c r="W44">
-        <v>0.06119999999999999</v>
+        <v>0.1038320526022084</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y44">
-        <v>1.527465061264087</v>
+        <v>0.9146787167445425</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1184236596749217</v>
+        <v>0.1194336596749217</v>
       </c>
       <c r="C45">
-        <v>485.21324877836</v>
+        <v>457.1424544171908</v>
       </c>
       <c r="D45">
-        <v>977.8877124217381</v>
+        <v>964.4744637266939</v>
       </c>
       <c r="E45">
-        <v>490.819897030871</v>
+        <v>505.4774426969961</v>
       </c>
       <c r="F45">
-        <v>630.274463643378</v>
+        <v>644.9320093095031</v>
       </c>
       <c r="G45">
         <v>137.6</v>
@@ -4977,37 +4977,37 @@
         <v>84.63</v>
       </c>
       <c r="M45">
-        <v>92.5242912628479</v>
+        <v>94.67601896663506</v>
       </c>
       <c r="N45">
-        <v>-7.894291262847901</v>
+        <v>-10.04601896663506</v>
       </c>
       <c r="O45">
-        <v>-2.526173204111328</v>
+        <v>-3.214726069323219</v>
       </c>
       <c r="P45">
-        <v>-5.368118058736572</v>
+        <v>-6.83129289731184</v>
       </c>
       <c r="Q45">
-        <v>31.53188194126343</v>
+        <v>30.06870710268816</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1294313632560913</v>
+        <v>0.130924780457093</v>
       </c>
       <c r="T45">
-        <v>1.089997020768182</v>
+        <v>1.109461253281899</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.2926971893582536</v>
+        <v>0.2860449805092024</v>
       </c>
       <c r="W45">
-        <v>0.1038320526022084</v>
+        <v>0.1048085968612491</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.9146787167445425</v>
+        <v>0.8938905640912574</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1194336596749217</v>
+        <v>0.1204436596749217</v>
       </c>
       <c r="C46">
-        <v>457.1424544171908</v>
+        <v>429.4346481849797</v>
       </c>
       <c r="D46">
-        <v>964.4744637266939</v>
+        <v>951.4242031606079</v>
       </c>
       <c r="E46">
-        <v>505.4774426969961</v>
+        <v>520.1349883631212</v>
       </c>
       <c r="F46">
-        <v>644.9320093095031</v>
+        <v>659.5895549756282</v>
       </c>
       <c r="G46">
         <v>137.6</v>
@@ -5059,37 +5059,37 @@
         <v>84.63</v>
       </c>
       <c r="M46">
-        <v>94.67601896663506</v>
+        <v>96.82774667042223</v>
       </c>
       <c r="N46">
-        <v>-10.04601896663506</v>
+        <v>-12.19774667042223</v>
       </c>
       <c r="O46">
-        <v>-3.214726069323219</v>
+        <v>-3.903278934535115</v>
       </c>
       <c r="P46">
-        <v>-6.83129289731184</v>
+        <v>-8.294467735887119</v>
       </c>
       <c r="Q46">
-        <v>30.06870710268816</v>
+        <v>28.60553226411288</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.130924780457093</v>
+        <v>0.132472503738131</v>
       </c>
       <c r="T46">
-        <v>1.109461253281899</v>
+        <v>1.129633276068843</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.2860449805092024</v>
+        <v>0.2796884253867756</v>
       </c>
       <c r="W46">
-        <v>0.1048085968612491</v>
+        <v>0.1057417391532214</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8938905640912574</v>
+        <v>0.8740263293336739</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1204436596749217</v>
+        <v>0.1214536596749217</v>
       </c>
       <c r="C47">
-        <v>429.4346481849797</v>
+        <v>402.0752920668384</v>
       </c>
       <c r="D47">
-        <v>951.4242031606079</v>
+        <v>938.7223927085917</v>
       </c>
       <c r="E47">
-        <v>520.1349883631212</v>
+        <v>534.7925340292463</v>
       </c>
       <c r="F47">
-        <v>659.5895549756282</v>
+        <v>674.2471006417533</v>
       </c>
       <c r="G47">
         <v>137.6</v>
@@ -5141,37 +5141,37 @@
         <v>84.63</v>
       </c>
       <c r="M47">
-        <v>96.82774667042223</v>
+        <v>98.97947437420939</v>
       </c>
       <c r="N47">
-        <v>-12.19774667042223</v>
+        <v>-14.34947437420939</v>
       </c>
       <c r="O47">
-        <v>-3.903278934535115</v>
+        <v>-4.591831799747006</v>
       </c>
       <c r="P47">
-        <v>-8.294467735887119</v>
+        <v>-9.757642574462388</v>
       </c>
       <c r="Q47">
-        <v>28.60553226411288</v>
+        <v>27.14235742553761</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.132472503738131</v>
+        <v>0.134077550103652</v>
       </c>
       <c r="T47">
-        <v>1.129633276068843</v>
+        <v>1.150552410810858</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2796884253867756</v>
+        <v>0.2736082422261936</v>
       </c>
       <c r="W47">
-        <v>0.1057417391532214</v>
+        <v>0.1066343100411948</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8740263293336739</v>
+        <v>0.8550257569568548</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1214536596749217</v>
+        <v>0.1224636596749217</v>
       </c>
       <c r="C48">
-        <v>402.0752920668384</v>
+        <v>375.0506141681018</v>
       </c>
       <c r="D48">
-        <v>938.7223927085917</v>
+        <v>926.3552604759802</v>
       </c>
       <c r="E48">
-        <v>534.7925340292463</v>
+        <v>549.4500796953714</v>
       </c>
       <c r="F48">
-        <v>674.2471006417533</v>
+        <v>688.9046463078784</v>
       </c>
       <c r="G48">
         <v>137.6</v>
@@ -5223,37 +5223,37 @@
         <v>84.63</v>
       </c>
       <c r="M48">
-        <v>98.97947437420939</v>
+        <v>101.1312020779965</v>
       </c>
       <c r="N48">
-        <v>-14.34947437420939</v>
+        <v>-16.50120207799655</v>
       </c>
       <c r="O48">
-        <v>-4.591831799747006</v>
+        <v>-5.280384664958897</v>
       </c>
       <c r="P48">
-        <v>-9.757642574462388</v>
+        <v>-11.22081741303766</v>
       </c>
       <c r="Q48">
-        <v>27.14235742553761</v>
+        <v>25.67918258696234</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.134077550103652</v>
+        <v>0.1357431642565511</v>
       </c>
       <c r="T48">
-        <v>1.150552410810858</v>
+        <v>1.172260946863894</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2736082422261936</v>
+        <v>0.2677867902639341</v>
       </c>
       <c r="W48">
-        <v>0.1066343100411948</v>
+        <v>0.1074888991892545</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8550257569568548</v>
+        <v>0.8368337195747941</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1224636596749217</v>
+        <v>0.1234736596749217</v>
       </c>
       <c r="C49">
-        <v>375.0506141681018</v>
+        <v>348.3475589045601</v>
       </c>
       <c r="D49">
-        <v>926.3552604759802</v>
+        <v>914.3097508785635</v>
       </c>
       <c r="E49">
-        <v>549.4500796953714</v>
+        <v>564.1076253614965</v>
       </c>
       <c r="F49">
-        <v>688.9046463078784</v>
+        <v>703.5621919740034</v>
       </c>
       <c r="G49">
         <v>137.6</v>
@@ -5305,37 +5305,37 @@
         <v>84.63</v>
       </c>
       <c r="M49">
-        <v>101.1312020779965</v>
+        <v>103.2829297817837</v>
       </c>
       <c r="N49">
-        <v>-16.50120207799655</v>
+        <v>-18.65292978178373</v>
       </c>
       <c r="O49">
-        <v>-5.280384664958897</v>
+        <v>-5.968937530170792</v>
       </c>
       <c r="P49">
-        <v>-11.22081741303766</v>
+        <v>-12.68399225161293</v>
       </c>
       <c r="Q49">
-        <v>25.67918258696234</v>
+        <v>24.21600774838706</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1357431642565511</v>
+        <v>0.137472840492254</v>
       </c>
       <c r="T49">
-        <v>1.172260946863894</v>
+        <v>1.194804426611276</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2677867902639341</v>
+        <v>0.2622078988001021</v>
       </c>
       <c r="W49">
-        <v>0.1074888991892545</v>
+        <v>0.108307880456145</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8368337195747941</v>
+        <v>0.8193996837503191</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1234736596749217</v>
+        <v>0.1244836596749217</v>
       </c>
       <c r="C50">
-        <v>348.3475589045602</v>
+        <v>321.9537410288995</v>
       </c>
       <c r="D50">
-        <v>914.3097508785635</v>
+        <v>902.5734786690278</v>
       </c>
       <c r="E50">
-        <v>564.1076253614963</v>
+        <v>578.7651710276214</v>
       </c>
       <c r="F50">
-        <v>703.5621919740033</v>
+        <v>718.2197376401284</v>
       </c>
       <c r="G50">
         <v>137.6</v>
@@ -5387,37 +5387,37 @@
         <v>84.63</v>
       </c>
       <c r="M50">
-        <v>103.2829297817837</v>
+        <v>105.4346574855709</v>
       </c>
       <c r="N50">
-        <v>-18.6529297817837</v>
+        <v>-20.80465748557087</v>
       </c>
       <c r="O50">
-        <v>-5.968937530170783</v>
+        <v>-6.657490395382679</v>
       </c>
       <c r="P50">
-        <v>-12.68399225161291</v>
+        <v>-14.14716709018819</v>
       </c>
       <c r="Q50">
-        <v>24.21600774838709</v>
+        <v>22.75283290981181</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.137472840492254</v>
+        <v>0.1392703471685727</v>
       </c>
       <c r="T50">
-        <v>1.194804426611276</v>
+        <v>1.218231964387968</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2622078988001022</v>
+        <v>0.2568567171919368</v>
       </c>
       <c r="W50">
-        <v>0.108307880456145</v>
+        <v>0.1090934339162237</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8193996837503194</v>
+        <v>0.8026772412248024</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1244836596749217</v>
+        <v>0.1543394399202351</v>
       </c>
       <c r="C51">
-        <v>321.9537410288995</v>
+        <v>59.02666813659937</v>
       </c>
       <c r="D51">
-        <v>902.5734786690278</v>
+        <v>654.3039514428528</v>
       </c>
       <c r="E51">
-        <v>578.7651710276214</v>
+        <v>593.4227166937465</v>
       </c>
       <c r="F51">
-        <v>718.2197376401284</v>
+        <v>732.8772833062535</v>
       </c>
       <c r="G51">
         <v>137.6</v>
@@ -5469,45 +5469,45 @@
         <v>84.63</v>
       </c>
       <c r="M51">
-        <v>105.4346574855709</v>
+        <v>147.1617584878957</v>
       </c>
       <c r="N51">
-        <v>-20.80465748557087</v>
+        <v>-62.5317584878957</v>
       </c>
       <c r="O51">
-        <v>-6.657490395382679</v>
+        <v>-20.01016271612663</v>
       </c>
       <c r="P51">
-        <v>-14.14716709018819</v>
+        <v>-42.52159577176907</v>
       </c>
       <c r="Q51">
-        <v>22.75283290981181</v>
+        <v>-5.621595771769073</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1392703471685727</v>
+        <v>0.1448313146025711</v>
       </c>
       <c r="T51">
-        <v>1.218231964387968</v>
+        <v>1.290710012092226</v>
       </c>
       <c r="U51">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.2568567171919368</v>
+        <v>0.1840260695323745</v>
       </c>
       <c r="W51">
-        <v>0.1090934339162237</v>
+        <v>0.1638475652378992</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.8026772412248024</v>
+        <v>0.5750814672886704</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1543394399202351</v>
+        <v>0.1558894399202351</v>
       </c>
       <c r="C52">
-        <v>59.02666813659937</v>
+        <v>35.1568753605676</v>
       </c>
       <c r="D52">
-        <v>654.3039514428528</v>
+        <v>645.0917043329462</v>
       </c>
       <c r="E52">
-        <v>593.4227166937465</v>
+        <v>608.0802623598715</v>
       </c>
       <c r="F52">
-        <v>732.8772833062535</v>
+        <v>747.5348289723786</v>
       </c>
       <c r="G52">
         <v>137.6</v>
@@ -5551,37 +5551,37 @@
         <v>84.63</v>
       </c>
       <c r="M52">
-        <v>147.1617584878957</v>
+        <v>150.1049936576536</v>
       </c>
       <c r="N52">
-        <v>-62.5317584878957</v>
+        <v>-65.47499365765364</v>
       </c>
       <c r="O52">
-        <v>-20.01016271612663</v>
+        <v>-20.95199797044917</v>
       </c>
       <c r="P52">
-        <v>-42.52159577176907</v>
+        <v>-44.52299568720447</v>
       </c>
       <c r="Q52">
-        <v>-5.621595771769073</v>
+        <v>-7.622995687204472</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1448313146025711</v>
+        <v>0.1468523618393582</v>
       </c>
       <c r="T52">
-        <v>1.290710012092226</v>
+        <v>1.317051032747169</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1840260695323745</v>
+        <v>0.1804177152278181</v>
       </c>
       <c r="W52">
-        <v>0.1638475652378992</v>
+        <v>0.1645721227822541</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5750814672886704</v>
+        <v>0.5638053600869316</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1558894399202351</v>
+        <v>0.1574394399202351</v>
       </c>
       <c r="C53">
-        <v>35.1568753605676</v>
+        <v>11.5428879348774</v>
       </c>
       <c r="D53">
-        <v>645.0917043329462</v>
+        <v>636.1352625733811</v>
       </c>
       <c r="E53">
-        <v>608.0802623598715</v>
+        <v>622.7378080259966</v>
       </c>
       <c r="F53">
-        <v>747.5348289723786</v>
+        <v>762.1923746385037</v>
       </c>
       <c r="G53">
         <v>137.6</v>
@@ -5633,37 +5633,37 @@
         <v>84.63</v>
       </c>
       <c r="M53">
-        <v>150.1049936576536</v>
+        <v>153.0482288274115</v>
       </c>
       <c r="N53">
-        <v>-65.47499365765364</v>
+        <v>-68.41822882741155</v>
       </c>
       <c r="O53">
-        <v>-20.95199797044917</v>
+        <v>-21.8938332247717</v>
       </c>
       <c r="P53">
-        <v>-44.52299568720447</v>
+        <v>-46.52439560263986</v>
       </c>
       <c r="Q53">
-        <v>-7.622995687204472</v>
+        <v>-9.624395602639858</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1468523618393582</v>
+        <v>0.1489576193776782</v>
       </c>
       <c r="T53">
-        <v>1.317051032747169</v>
+        <v>1.344489595929402</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1804177152278181</v>
+        <v>0.1769481437811293</v>
       </c>
       <c r="W53">
-        <v>0.1645721227822541</v>
+        <v>0.1652688127287492</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5638053600869316</v>
+        <v>0.5529629493160291</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1574394399202351</v>
+        <v>0.1589894399202351</v>
       </c>
       <c r="C54">
-        <v>11.5428879348774</v>
+        <v>-11.82580302610552</v>
       </c>
       <c r="D54">
-        <v>636.1352625733811</v>
+        <v>627.4241172785232</v>
       </c>
       <c r="E54">
-        <v>622.7378080259966</v>
+        <v>637.3953536921217</v>
       </c>
       <c r="F54">
-        <v>762.1923746385037</v>
+        <v>776.8499203046288</v>
       </c>
       <c r="G54">
         <v>137.6</v>
@@ -5715,37 +5715,37 @@
         <v>84.63</v>
       </c>
       <c r="M54">
-        <v>153.0482288274115</v>
+        <v>155.9914639971695</v>
       </c>
       <c r="N54">
-        <v>-68.41822882741155</v>
+        <v>-71.36146399716947</v>
       </c>
       <c r="O54">
-        <v>-21.8938332247717</v>
+        <v>-22.83566847909423</v>
       </c>
       <c r="P54">
-        <v>-46.52439560263986</v>
+        <v>-48.52579551807523</v>
       </c>
       <c r="Q54">
-        <v>-9.624395602639858</v>
+        <v>-11.62579551807524</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1489576193776782</v>
+        <v>0.1511524623431607</v>
       </c>
       <c r="T54">
-        <v>1.344489595929402</v>
+        <v>1.373095757544921</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1769481437811293</v>
+        <v>0.1736094995588439</v>
       </c>
       <c r="W54">
-        <v>0.1652688127287492</v>
+        <v>0.1659392124885841</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5529629493160291</v>
+        <v>0.5425296861213871</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1589894399202351</v>
+        <v>0.1605394399202351</v>
       </c>
       <c r="C55">
-        <v>-11.82580302610552</v>
+        <v>-34.95913855540061</v>
       </c>
       <c r="D55">
-        <v>627.4241172785232</v>
+        <v>618.9483274153532</v>
       </c>
       <c r="E55">
-        <v>637.3953536921217</v>
+        <v>652.0528993582468</v>
       </c>
       <c r="F55">
-        <v>776.8499203046288</v>
+        <v>791.5074659707539</v>
       </c>
       <c r="G55">
         <v>137.6</v>
@@ -5797,37 +5797,37 @@
         <v>84.63</v>
       </c>
       <c r="M55">
-        <v>155.9914639971695</v>
+        <v>158.9346991669274</v>
       </c>
       <c r="N55">
-        <v>-71.36146399716947</v>
+        <v>-74.30469916692738</v>
       </c>
       <c r="O55">
-        <v>-22.83566847909423</v>
+        <v>-23.77750373341676</v>
       </c>
       <c r="P55">
-        <v>-48.52579551807523</v>
+        <v>-50.52719543351061</v>
       </c>
       <c r="Q55">
-        <v>-11.62579551807524</v>
+        <v>-13.62719543351061</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1511524623431607</v>
+        <v>0.1534427332636642</v>
       </c>
       <c r="T55">
-        <v>1.373095757544921</v>
+        <v>1.402945665317637</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1736094995588439</v>
+        <v>0.1703945088262727</v>
       </c>
       <c r="W55">
-        <v>0.1659392124885841</v>
+        <v>0.1665847826276844</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5425296861213871</v>
+        <v>0.5324828400821021</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1605394399202351</v>
+        <v>0.1620894399202352</v>
       </c>
       <c r="C56">
-        <v>-34.95913855540061</v>
+        <v>-57.86652967741441</v>
       </c>
       <c r="D56">
-        <v>618.9483274153532</v>
+        <v>610.6984819594645</v>
       </c>
       <c r="E56">
-        <v>652.0528993582468</v>
+        <v>666.7104450243719</v>
       </c>
       <c r="F56">
-        <v>791.5074659707539</v>
+        <v>806.1650116368789</v>
       </c>
       <c r="G56">
         <v>137.6</v>
@@ -5879,37 +5879,37 @@
         <v>84.63</v>
       </c>
       <c r="M56">
-        <v>158.9346991669274</v>
+        <v>161.8779343366853</v>
       </c>
       <c r="N56">
-        <v>-74.30469916692738</v>
+        <v>-77.24793433668529</v>
       </c>
       <c r="O56">
-        <v>-23.77750373341676</v>
+        <v>-24.71933898773929</v>
       </c>
       <c r="P56">
-        <v>-50.52719543351061</v>
+        <v>-52.528595348946</v>
       </c>
       <c r="Q56">
-        <v>-13.62719543351061</v>
+        <v>-15.628595348946</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1534427332636642</v>
+        <v>0.1558347940028567</v>
       </c>
       <c r="T56">
-        <v>1.402945665317637</v>
+        <v>1.434122235658029</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1703945088262727</v>
+        <v>0.1672964268476132</v>
       </c>
       <c r="W56">
-        <v>0.1665847826276844</v>
+        <v>0.1672068774889993</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5324828400821021</v>
+        <v>0.5228013338987911</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1620894399202352</v>
+        <v>0.1636394399202351</v>
       </c>
       <c r="C57">
-        <v>-57.86652967741441</v>
+        <v>-80.55689226525851</v>
       </c>
       <c r="D57">
-        <v>610.6984819594645</v>
+        <v>602.6656650377455</v>
       </c>
       <c r="E57">
-        <v>666.7104450243719</v>
+        <v>681.367990690497</v>
       </c>
       <c r="F57">
-        <v>806.1650116368789</v>
+        <v>820.822557303004</v>
       </c>
       <c r="G57">
         <v>137.6</v>
@@ -5961,37 +5961,37 @@
         <v>84.63</v>
       </c>
       <c r="M57">
-        <v>161.8779343366853</v>
+        <v>164.8211695064432</v>
       </c>
       <c r="N57">
-        <v>-77.24793433668529</v>
+        <v>-80.19116950644323</v>
       </c>
       <c r="O57">
-        <v>-24.71933898773929</v>
+        <v>-25.66117424206183</v>
       </c>
       <c r="P57">
-        <v>-52.528595348946</v>
+        <v>-54.5299952643814</v>
       </c>
       <c r="Q57">
-        <v>-15.628595348946</v>
+        <v>-17.6299952643814</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1558347940028567</v>
+        <v>0.1583355847756489</v>
       </c>
       <c r="T57">
-        <v>1.434122235658029</v>
+        <v>1.466715922832075</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1672964268476132</v>
+        <v>0.1643089906539058</v>
       </c>
       <c r="W57">
-        <v>0.1672068774889993</v>
+        <v>0.1678067546766957</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5228013338987911</v>
+        <v>0.5134655957934555</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1636394399202351</v>
+        <v>0.1651894399202352</v>
       </c>
       <c r="C58">
-        <v>-80.55689226525851</v>
+        <v>-103.0386791828093</v>
       </c>
       <c r="D58">
-        <v>602.6656650377455</v>
+        <v>594.8414237863198</v>
       </c>
       <c r="E58">
-        <v>681.367990690497</v>
+        <v>696.0255363566221</v>
       </c>
       <c r="F58">
-        <v>820.822557303004</v>
+        <v>835.4801029691291</v>
       </c>
       <c r="G58">
         <v>137.6</v>
@@ -6043,37 +6043,37 @@
         <v>84.63</v>
       </c>
       <c r="M58">
-        <v>164.8211695064432</v>
+        <v>167.7644046762011</v>
       </c>
       <c r="N58">
-        <v>-80.19116950644323</v>
+        <v>-83.13440467620114</v>
       </c>
       <c r="O58">
-        <v>-25.66117424206183</v>
+        <v>-26.60300949638437</v>
       </c>
       <c r="P58">
-        <v>-54.5299952643814</v>
+        <v>-56.53139517981678</v>
       </c>
       <c r="Q58">
-        <v>-17.6299952643814</v>
+        <v>-19.63139517981678</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1583355847756489</v>
+        <v>0.1609526913983385</v>
       </c>
       <c r="T58">
-        <v>1.466715922832075</v>
+        <v>1.500825595456077</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1643089906539058</v>
+        <v>0.1614263767827846</v>
       </c>
       <c r="W58">
-        <v>0.1678067546766957</v>
+        <v>0.1683855835420169</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5134655957934555</v>
+        <v>0.5044574274462019</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1651894399202352</v>
+        <v>0.1877842345437721</v>
       </c>
       <c r="C59">
-        <v>-103.0386791828093</v>
+        <v>-212.3568739499492</v>
       </c>
       <c r="D59">
-        <v>594.8414237863198</v>
+        <v>500.180774685305</v>
       </c>
       <c r="E59">
-        <v>696.0255363566221</v>
+        <v>710.6830820227472</v>
       </c>
       <c r="F59">
-        <v>835.4801029691291</v>
+        <v>850.1376486352542</v>
       </c>
       <c r="G59">
         <v>137.6</v>
@@ -6125,45 +6125,45 @@
         <v>84.63</v>
       </c>
       <c r="M59">
-        <v>167.7644046762011</v>
+        <v>200.462457548193</v>
       </c>
       <c r="N59">
-        <v>-83.13440467620114</v>
+        <v>-115.832457548193</v>
       </c>
       <c r="O59">
-        <v>-26.60300949638437</v>
+        <v>-37.06638641542175</v>
       </c>
       <c r="P59">
-        <v>-56.53139517981678</v>
+        <v>-78.76607113277122</v>
       </c>
       <c r="Q59">
-        <v>-19.63139517981678</v>
+        <v>-41.86607113277122</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1609526913983385</v>
+        <v>0.1654677426781488</v>
       </c>
       <c r="T59">
-        <v>1.500825595456077</v>
+        <v>1.559671849445011</v>
       </c>
       <c r="U59">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1614263767827846</v>
+        <v>0.1350956200538913</v>
       </c>
       <c r="W59">
-        <v>0.1683855835420169</v>
+        <v>0.2039444527912924</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.5044574274462019</v>
+        <v>0.4221738126684105</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1877842345437721</v>
+        <v>0.1896842345437721</v>
       </c>
       <c r="C60">
-        <v>-212.356873949949</v>
+        <v>-233.6193369297424</v>
       </c>
       <c r="D60">
-        <v>500.180774685305</v>
+        <v>493.5758573716367</v>
       </c>
       <c r="E60">
-        <v>710.6830820227469</v>
+        <v>725.340627688872</v>
       </c>
       <c r="F60">
-        <v>850.137648635254</v>
+        <v>864.7951943013791</v>
       </c>
       <c r="G60">
         <v>137.6</v>
@@ -6207,37 +6207,37 @@
         <v>84.63</v>
       </c>
       <c r="M60">
-        <v>200.4624575481929</v>
+        <v>203.9187068162652</v>
       </c>
       <c r="N60">
-        <v>-115.8324575481929</v>
+        <v>-119.2887068162652</v>
       </c>
       <c r="O60">
-        <v>-37.06638641542173</v>
+        <v>-38.17238618120486</v>
       </c>
       <c r="P60">
-        <v>-78.76607113277117</v>
+        <v>-81.11632063506033</v>
       </c>
       <c r="Q60">
-        <v>-41.86607113277118</v>
+        <v>-44.21632063506033</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1654677426781487</v>
+        <v>0.1683864681093231</v>
       </c>
       <c r="T60">
-        <v>1.55967184944501</v>
+        <v>1.597712626260743</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1350956200538914</v>
+        <v>0.1328058637817915</v>
       </c>
       <c r="W60">
-        <v>0.2039444527912924</v>
+        <v>0.2044843773202536</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4221738126684106</v>
+        <v>0.4150183243180985</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1896842345437721</v>
+        <v>0.1915842345437721</v>
       </c>
       <c r="C61">
-        <v>-233.6193369297424</v>
+        <v>-254.7096366720604</v>
       </c>
       <c r="D61">
-        <v>493.5758573716367</v>
+        <v>487.1431032954438</v>
       </c>
       <c r="E61">
-        <v>725.340627688872</v>
+        <v>739.9981733549971</v>
       </c>
       <c r="F61">
-        <v>864.7951943013791</v>
+        <v>879.4527399675042</v>
       </c>
       <c r="G61">
         <v>137.6</v>
@@ -6289,37 +6289,37 @@
         <v>84.63</v>
       </c>
       <c r="M61">
-        <v>203.9187068162652</v>
+        <v>207.3749560843375</v>
       </c>
       <c r="N61">
-        <v>-119.2887068162652</v>
+        <v>-122.7449560843375</v>
       </c>
       <c r="O61">
-        <v>-38.17238618120486</v>
+        <v>-39.278385946988</v>
       </c>
       <c r="P61">
-        <v>-81.11632063506033</v>
+        <v>-83.46657013734949</v>
       </c>
       <c r="Q61">
-        <v>-44.21632063506033</v>
+        <v>-46.56657013734949</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1683864681093231</v>
+        <v>0.1714511298120562</v>
       </c>
       <c r="T61">
-        <v>1.597712626260743</v>
+        <v>1.637655441917261</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1328058637817915</v>
+        <v>0.1305924327187617</v>
       </c>
       <c r="W61">
-        <v>0.2044843773202536</v>
+        <v>0.205006304364916</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4150183243180985</v>
+        <v>0.4081013522461302</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1915842345437721</v>
+        <v>0.1934842345437721</v>
       </c>
       <c r="C62">
-        <v>-254.7096366720604</v>
+        <v>-275.6344179650662</v>
       </c>
       <c r="D62">
-        <v>487.1431032954438</v>
+        <v>480.8758676685631</v>
       </c>
       <c r="E62">
-        <v>739.9981733549971</v>
+        <v>754.6557190211222</v>
       </c>
       <c r="F62">
-        <v>879.4527399675042</v>
+        <v>894.1102856336292</v>
       </c>
       <c r="G62">
         <v>137.6</v>
@@ -6371,37 +6371,37 @@
         <v>84.63</v>
       </c>
       <c r="M62">
-        <v>207.3749560843375</v>
+        <v>210.8312053524098</v>
       </c>
       <c r="N62">
-        <v>-122.7449560843375</v>
+        <v>-126.2012053524098</v>
       </c>
       <c r="O62">
-        <v>-39.278385946988</v>
+        <v>-40.38438571277113</v>
       </c>
       <c r="P62">
-        <v>-83.46657013734949</v>
+        <v>-85.81681963963867</v>
       </c>
       <c r="Q62">
-        <v>-46.56657013734949</v>
+        <v>-48.91681963963867</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1714511298120562</v>
+        <v>0.1746729536533909</v>
       </c>
       <c r="T62">
-        <v>1.637655441917261</v>
+        <v>1.679646607094627</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1305924327187617</v>
+        <v>0.1284515731659951</v>
       </c>
       <c r="W62">
-        <v>0.205006304364916</v>
+        <v>0.2055111190474584</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4081013522461302</v>
+        <v>0.4014111661437346</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1934842345437721</v>
+        <v>0.1953842345437721</v>
       </c>
       <c r="C63">
-        <v>-275.6344179650662</v>
+        <v>-296.399987991893</v>
       </c>
       <c r="D63">
-        <v>480.8758676685631</v>
+        <v>474.7678433078613</v>
       </c>
       <c r="E63">
-        <v>754.6557190211222</v>
+        <v>769.3132646872473</v>
       </c>
       <c r="F63">
-        <v>894.1102856336292</v>
+        <v>908.7678312997543</v>
       </c>
       <c r="G63">
         <v>137.6</v>
@@ -6453,37 +6453,37 @@
         <v>84.63</v>
       </c>
       <c r="M63">
-        <v>210.8312053524098</v>
+        <v>214.2874546204821</v>
       </c>
       <c r="N63">
-        <v>-126.2012053524098</v>
+        <v>-129.6574546204821</v>
       </c>
       <c r="O63">
-        <v>-40.38438571277113</v>
+        <v>-41.49038547855427</v>
       </c>
       <c r="P63">
-        <v>-85.81681963963867</v>
+        <v>-88.16706914192783</v>
       </c>
       <c r="Q63">
-        <v>-48.91681963963867</v>
+        <v>-51.26706914192783</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1746729536533909</v>
+        <v>0.1780643471705854</v>
       </c>
       <c r="T63">
-        <v>1.679646607094627</v>
+        <v>1.723847833597117</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1284515731659951</v>
+        <v>0.1263797735988016</v>
       </c>
       <c r="W63">
-        <v>0.2055111190474584</v>
+        <v>0.2059996493854026</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4014111661437346</v>
+        <v>0.394936792496255</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1953842345437721</v>
+        <v>0.1972842345437721</v>
       </c>
       <c r="C64">
-        <v>-296.399987991893</v>
+        <v>-317.012337502799</v>
       </c>
       <c r="D64">
-        <v>474.7678433078613</v>
+        <v>468.8130394630804</v>
       </c>
       <c r="E64">
-        <v>769.3132646872473</v>
+        <v>783.9708103533724</v>
       </c>
       <c r="F64">
-        <v>908.7678312997543</v>
+        <v>923.4253769658794</v>
       </c>
       <c r="G64">
         <v>137.6</v>
@@ -6535,37 +6535,37 @@
         <v>84.63</v>
       </c>
       <c r="M64">
-        <v>214.2874546204821</v>
+        <v>217.7437038885544</v>
       </c>
       <c r="N64">
-        <v>-129.6574546204821</v>
+        <v>-133.1137038885544</v>
       </c>
       <c r="O64">
-        <v>-41.49038547855427</v>
+        <v>-42.5963852443374</v>
       </c>
       <c r="P64">
-        <v>-88.16706914192783</v>
+        <v>-90.51731864421697</v>
       </c>
       <c r="Q64">
-        <v>-51.26706914192783</v>
+        <v>-53.61731864421697</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1780643471705854</v>
+        <v>0.1816390592562769</v>
       </c>
       <c r="T64">
-        <v>1.723847833597117</v>
+        <v>1.770438315586228</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1263797735988016</v>
+        <v>0.1243737454464397</v>
       </c>
       <c r="W64">
-        <v>0.2059996493854026</v>
+        <v>0.2064726708237296</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.394936792496255</v>
+        <v>0.388667954520124</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1972842345437721</v>
+        <v>0.1991842345437721</v>
       </c>
       <c r="C65">
-        <v>-317.012337502799</v>
+        <v>-337.477160413742</v>
       </c>
       <c r="D65">
-        <v>468.8130394630804</v>
+        <v>463.0057622182625</v>
       </c>
       <c r="E65">
-        <v>783.9708103533724</v>
+        <v>798.6283560194975</v>
       </c>
       <c r="F65">
-        <v>923.4253769658794</v>
+        <v>938.0829226320045</v>
       </c>
       <c r="G65">
         <v>137.6</v>
@@ -6617,37 +6617,37 @@
         <v>84.63</v>
       </c>
       <c r="M65">
-        <v>217.7437038885544</v>
+        <v>221.1999531566267</v>
       </c>
       <c r="N65">
-        <v>-133.1137038885544</v>
+        <v>-136.5699531566267</v>
       </c>
       <c r="O65">
-        <v>-42.5963852443374</v>
+        <v>-43.70238501012054</v>
       </c>
       <c r="P65">
-        <v>-90.51731864421697</v>
+        <v>-92.86756814650613</v>
       </c>
       <c r="Q65">
-        <v>-53.61731864421697</v>
+        <v>-55.96756814650613</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1816390592562769</v>
+        <v>0.1854123664578402</v>
       </c>
       <c r="T65">
-        <v>1.770438315586228</v>
+        <v>1.819617157685846</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1243737454464397</v>
+        <v>0.1224304056738391</v>
       </c>
       <c r="W65">
-        <v>0.2064726708237296</v>
+        <v>0.2069309103421088</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.388667954520124</v>
+        <v>0.382595017730747</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1991842345437721</v>
+        <v>0.2010842345437721</v>
       </c>
       <c r="C66">
-        <v>-337.477160413742</v>
+        <v>-357.7998719661482</v>
       </c>
       <c r="D66">
-        <v>463.0057622182625</v>
+        <v>457.3405963319814</v>
       </c>
       <c r="E66">
-        <v>798.6283560194975</v>
+        <v>813.2859016856225</v>
       </c>
       <c r="F66">
-        <v>938.0829226320045</v>
+        <v>952.7404682981296</v>
       </c>
       <c r="G66">
         <v>137.6</v>
@@ -6699,37 +6699,37 @@
         <v>84.63</v>
       </c>
       <c r="M66">
-        <v>221.1999531566267</v>
+        <v>224.656202424699</v>
       </c>
       <c r="N66">
-        <v>-136.5699531566267</v>
+        <v>-140.026202424699</v>
       </c>
       <c r="O66">
-        <v>-43.70238501012054</v>
+        <v>-44.80838477590367</v>
       </c>
       <c r="P66">
-        <v>-92.86756814650613</v>
+        <v>-95.21781764879529</v>
       </c>
       <c r="Q66">
-        <v>-55.96756814650613</v>
+        <v>-58.31781764879529</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1854123664578402</v>
+        <v>0.1894012912137785</v>
       </c>
       <c r="T66">
-        <v>1.819617157685846</v>
+        <v>1.871606219334013</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1224304056738391</v>
+        <v>0.1205468609711646</v>
       </c>
       <c r="W66">
-        <v>0.2069309103421088</v>
+        <v>0.2073750501829994</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.382595017730747</v>
+        <v>0.3767089405348893</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2010842345437721</v>
+        <v>0.2029842345437721</v>
       </c>
       <c r="C67">
-        <v>-357.7998719661482</v>
+        <v>-377.9856255696209</v>
       </c>
       <c r="D67">
-        <v>457.3405963319814</v>
+        <v>451.8123883946338</v>
       </c>
       <c r="E67">
-        <v>813.2859016856225</v>
+        <v>827.9434473517476</v>
       </c>
       <c r="F67">
-        <v>952.7404682981296</v>
+        <v>967.3980139642547</v>
       </c>
       <c r="G67">
         <v>137.6</v>
@@ -6781,37 +6781,37 @@
         <v>84.63</v>
       </c>
       <c r="M67">
-        <v>224.656202424699</v>
+        <v>228.1124516927713</v>
       </c>
       <c r="N67">
-        <v>-140.026202424699</v>
+        <v>-143.4824516927713</v>
       </c>
       <c r="O67">
-        <v>-44.80838477590367</v>
+        <v>-45.91438454168681</v>
       </c>
       <c r="P67">
-        <v>-95.21781764879529</v>
+        <v>-97.56806715108445</v>
       </c>
       <c r="Q67">
-        <v>-58.31781764879529</v>
+        <v>-60.66806715108445</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1894012912137785</v>
+        <v>0.193624858602419</v>
       </c>
       <c r="T67">
-        <v>1.871606219334013</v>
+        <v>1.926653461079131</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1205468609711646</v>
+        <v>0.1187203933806924</v>
       </c>
       <c r="W67">
-        <v>0.2073750501829994</v>
+        <v>0.2078057312408327</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3767089405348893</v>
+        <v>0.3710012293146638</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2029842345437721</v>
+        <v>0.2048842345437721</v>
       </c>
       <c r="C68">
-        <v>-377.9856255696209</v>
+        <v>-398.0393284376942</v>
       </c>
       <c r="D68">
-        <v>451.8123883946338</v>
+        <v>446.4162311926856</v>
       </c>
       <c r="E68">
-        <v>827.9434473517476</v>
+        <v>842.6009930178727</v>
       </c>
       <c r="F68">
-        <v>967.3980139642547</v>
+        <v>982.0555596303798</v>
       </c>
       <c r="G68">
         <v>137.6</v>
@@ -6863,37 +6863,37 @@
         <v>84.63</v>
       </c>
       <c r="M68">
-        <v>228.1124516927713</v>
+        <v>231.5687009608436</v>
       </c>
       <c r="N68">
-        <v>-143.4824516927713</v>
+        <v>-146.9387009608436</v>
       </c>
       <c r="O68">
-        <v>-45.91438454168681</v>
+        <v>-47.02038430746994</v>
       </c>
       <c r="P68">
-        <v>-97.56806715108445</v>
+        <v>-99.91831665337362</v>
       </c>
       <c r="Q68">
-        <v>-60.66806715108445</v>
+        <v>-63.01831665337362</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.193624858602419</v>
+        <v>0.1981043997721893</v>
       </c>
       <c r="T68">
-        <v>1.926653461079131</v>
+        <v>1.98503689929365</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1187203933806924</v>
+        <v>0.1169484472108313</v>
       </c>
       <c r="W68">
-        <v>0.2078057312408327</v>
+        <v>0.208223556147686</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3710012293146638</v>
+        <v>0.3654638975338479</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2048842345437721</v>
+        <v>0.2067842345437721</v>
       </c>
       <c r="C69">
-        <v>-398.0393284376942</v>
+        <v>-417.9656561163553</v>
       </c>
       <c r="D69">
-        <v>446.4162311926856</v>
+        <v>441.1474491801496</v>
       </c>
       <c r="E69">
-        <v>842.6009930178727</v>
+        <v>857.2585386839978</v>
       </c>
       <c r="F69">
-        <v>982.0555596303798</v>
+        <v>996.7131052965049</v>
       </c>
       <c r="G69">
         <v>137.6</v>
@@ -6945,37 +6945,37 @@
         <v>84.63</v>
       </c>
       <c r="M69">
-        <v>231.5687009608436</v>
+        <v>235.0249502289159</v>
       </c>
       <c r="N69">
-        <v>-146.9387009608436</v>
+        <v>-150.3949502289159</v>
       </c>
       <c r="O69">
-        <v>-47.02038430746994</v>
+        <v>-48.12638407325308</v>
       </c>
       <c r="P69">
-        <v>-99.91831665337362</v>
+        <v>-102.2685661556628</v>
       </c>
       <c r="Q69">
-        <v>-63.01831665337362</v>
+        <v>-65.36856615566279</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1981043997721893</v>
+        <v>0.2028639122650702</v>
       </c>
       <c r="T69">
-        <v>1.98503689929365</v>
+        <v>2.047069302396577</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1169484472108313</v>
+        <v>0.1152286171047897</v>
       </c>
       <c r="W69">
-        <v>0.208223556147686</v>
+        <v>0.2086290920866906</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3654638975338479</v>
+        <v>0.3600894284524677</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2067842345437721</v>
+        <v>0.2086842345437721</v>
       </c>
       <c r="C70">
-        <v>-417.9656561163553</v>
+        <v>-437.7690659957358</v>
       </c>
       <c r="D70">
-        <v>441.1474491801496</v>
+        <v>436.0015849668942</v>
       </c>
       <c r="E70">
-        <v>857.2585386839978</v>
+        <v>871.9160843501229</v>
       </c>
       <c r="F70">
-        <v>996.7131052965049</v>
+        <v>1011.37065096263</v>
       </c>
       <c r="G70">
         <v>137.6</v>
@@ -7027,37 +7027,37 @@
         <v>84.63</v>
       </c>
       <c r="M70">
-        <v>235.0249502289159</v>
+        <v>238.4811994969882</v>
       </c>
       <c r="N70">
-        <v>-150.3949502289159</v>
+        <v>-153.8511994969882</v>
       </c>
       <c r="O70">
-        <v>-48.12638407325308</v>
+        <v>-49.23238383903621</v>
       </c>
       <c r="P70">
-        <v>-102.2685661556628</v>
+        <v>-104.618815657952</v>
       </c>
       <c r="Q70">
-        <v>-65.36856615566279</v>
+        <v>-67.71881565795195</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2028639122650702</v>
+        <v>0.2079304900800725</v>
       </c>
       <c r="T70">
-        <v>2.047069302396577</v>
+        <v>2.113103796022273</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1152286171047897</v>
+        <v>0.1135586371467493</v>
       </c>
       <c r="W70">
-        <v>0.2086290920866906</v>
+        <v>0.2090228733607965</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3600894284524677</v>
+        <v>0.3548707410835914</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2086842345437721</v>
+        <v>0.2105842345437721</v>
       </c>
       <c r="C71">
-        <v>-437.7690659957358</v>
+        <v>-457.4538098870469</v>
       </c>
       <c r="D71">
-        <v>436.0015849668942</v>
+        <v>430.9743867417082</v>
       </c>
       <c r="E71">
-        <v>871.9160843501229</v>
+        <v>886.573630016248</v>
       </c>
       <c r="F71">
-        <v>1011.37065096263</v>
+        <v>1026.028196628755</v>
       </c>
       <c r="G71">
         <v>137.6</v>
@@ -7109,37 +7109,37 @@
         <v>84.63</v>
       </c>
       <c r="M71">
-        <v>238.4811994969882</v>
+        <v>241.9374487650605</v>
       </c>
       <c r="N71">
-        <v>-153.8511994969882</v>
+        <v>-157.3074487650605</v>
       </c>
       <c r="O71">
-        <v>-49.23238383903621</v>
+        <v>-50.33838360481935</v>
       </c>
       <c r="P71">
-        <v>-104.618815657952</v>
+        <v>-106.9690651602411</v>
       </c>
       <c r="Q71">
-        <v>-67.71881565795195</v>
+        <v>-70.06906516024111</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2079304900800725</v>
+        <v>0.2133348397494083</v>
       </c>
       <c r="T71">
-        <v>2.113103796022273</v>
+        <v>2.183540589223016</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1135586371467493</v>
+        <v>0.1119363709017957</v>
       </c>
       <c r="W71">
-        <v>0.2090228733607965</v>
+        <v>0.2094054037413566</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3548707410835914</v>
+        <v>0.3498011590681115</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2105842345437721</v>
+        <v>0.2124842345437721</v>
       </c>
       <c r="C72">
-        <v>-457.4538098870469</v>
+        <v>-477.0239457393436</v>
       </c>
       <c r="D72">
-        <v>430.9743867417082</v>
+        <v>426.0617965555365</v>
       </c>
       <c r="E72">
-        <v>886.573630016248</v>
+        <v>901.2311756823731</v>
       </c>
       <c r="F72">
-        <v>1026.028196628755</v>
+        <v>1040.68574229488</v>
       </c>
       <c r="G72">
         <v>137.6</v>
@@ -7191,37 +7191,37 @@
         <v>84.63</v>
       </c>
       <c r="M72">
-        <v>241.9374487650605</v>
+        <v>245.3936980331328</v>
       </c>
       <c r="N72">
-        <v>-157.3074487650605</v>
+        <v>-160.7636980331328</v>
       </c>
       <c r="O72">
-        <v>-50.33838360481935</v>
+        <v>-51.44438337060248</v>
       </c>
       <c r="P72">
-        <v>-106.9690651602411</v>
+        <v>-109.3193146625303</v>
       </c>
       <c r="Q72">
-        <v>-70.06906516024111</v>
+        <v>-72.41931466253027</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2133348397494083</v>
+        <v>0.2191119031890431</v>
       </c>
       <c r="T72">
-        <v>2.183540589223016</v>
+        <v>2.258835092299672</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1119363709017957</v>
+        <v>0.110359802297545</v>
       </c>
       <c r="W72">
-        <v>0.2094054037413566</v>
+        <v>0.2097771586182389</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3498011590681115</v>
+        <v>0.3448743821798282</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2124842345437721</v>
+        <v>0.214384234543772</v>
       </c>
       <c r="C73">
-        <v>-477.0239457393434</v>
+        <v>-496.4833485639758</v>
       </c>
       <c r="D73">
-        <v>426.0617965555365</v>
+        <v>421.2599393970291</v>
       </c>
       <c r="E73">
-        <v>901.2311756823729</v>
+        <v>915.8887213484979</v>
       </c>
       <c r="F73">
-        <v>1040.68574229488</v>
+        <v>1055.343287961005</v>
       </c>
       <c r="G73">
         <v>137.6</v>
@@ -7273,37 +7273,37 @@
         <v>84.63</v>
       </c>
       <c r="M73">
-        <v>245.3936980331327</v>
+        <v>248.849947301205</v>
       </c>
       <c r="N73">
-        <v>-160.7636980331327</v>
+        <v>-164.219947301205</v>
       </c>
       <c r="O73">
-        <v>-51.44438337060247</v>
+        <v>-52.5503831363856</v>
       </c>
       <c r="P73">
-        <v>-109.3193146625302</v>
+        <v>-111.6695641648194</v>
       </c>
       <c r="Q73">
-        <v>-72.41931466253024</v>
+        <v>-74.7695641648194</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.219111903189043</v>
+        <v>0.2253016140172231</v>
       </c>
       <c r="T73">
-        <v>2.258835092299671</v>
+        <v>2.339507774167516</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1103598022975451</v>
+        <v>0.1088270272656347</v>
       </c>
       <c r="W73">
-        <v>0.2097771586182389</v>
+        <v>0.2101385869707633</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3448743821798284</v>
+        <v>0.3400844602051085</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.214384234543772</v>
+        <v>0.2162842345437721</v>
       </c>
       <c r="C74">
-        <v>-496.4833485639758</v>
+        <v>-515.8357206285434</v>
       </c>
       <c r="D74">
-        <v>421.2599393970291</v>
+        <v>416.5651129985867</v>
       </c>
       <c r="E74">
-        <v>915.8887213484979</v>
+        <v>930.546267014623</v>
       </c>
       <c r="F74">
-        <v>1055.343287961005</v>
+        <v>1070.00083362713</v>
       </c>
       <c r="G74">
         <v>137.6</v>
@@ -7355,37 +7355,37 @@
         <v>84.63</v>
       </c>
       <c r="M74">
-        <v>248.849947301205</v>
+        <v>252.3061965692773</v>
       </c>
       <c r="N74">
-        <v>-164.219947301205</v>
+        <v>-167.6761965692773</v>
       </c>
       <c r="O74">
-        <v>-52.5503831363856</v>
+        <v>-53.65638290216874</v>
       </c>
       <c r="P74">
-        <v>-111.6695641648194</v>
+        <v>-114.0198136671086</v>
       </c>
       <c r="Q74">
-        <v>-74.7695641648194</v>
+        <v>-77.11981366710856</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2253016140172231</v>
+        <v>0.2319498219437869</v>
       </c>
       <c r="T74">
-        <v>2.339507774167516</v>
+        <v>2.426156210247794</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1088270272656347</v>
+        <v>0.1073362460702151</v>
       </c>
       <c r="W74">
-        <v>0.2101385869707633</v>
+        <v>0.2104901131766433</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3400844602051085</v>
+        <v>0.3354257689694221</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2162842345437721</v>
+        <v>0.2181842345437721</v>
       </c>
       <c r="C75">
-        <v>-515.8357206285434</v>
+        <v>-535.0846009767059</v>
       </c>
       <c r="D75">
-        <v>416.5651129985867</v>
+        <v>411.9737783165492</v>
       </c>
       <c r="E75">
-        <v>930.546267014623</v>
+        <v>945.2038126807481</v>
       </c>
       <c r="F75">
-        <v>1070.00083362713</v>
+        <v>1084.658379293255</v>
       </c>
       <c r="G75">
         <v>137.6</v>
@@ -7437,37 +7437,37 @@
         <v>84.63</v>
       </c>
       <c r="M75">
-        <v>252.3061965692773</v>
+        <v>255.7624458373496</v>
       </c>
       <c r="N75">
-        <v>-167.6761965692773</v>
+        <v>-171.1324458373496</v>
       </c>
       <c r="O75">
-        <v>-53.65638290216874</v>
+        <v>-54.76238266795187</v>
       </c>
       <c r="P75">
-        <v>-114.0198136671086</v>
+        <v>-116.3700631693977</v>
       </c>
       <c r="Q75">
-        <v>-77.11981366710856</v>
+        <v>-79.47006316939772</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2319498219437869</v>
+        <v>0.2391094304800864</v>
       </c>
       <c r="T75">
-        <v>2.426156210247794</v>
+        <v>2.51946991064194</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1073362460702151</v>
+        <v>0.1058857562584554</v>
       </c>
       <c r="W75">
-        <v>0.2104901131766433</v>
+        <v>0.2108321386742562</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3354257689694221</v>
+        <v>0.3308929883076731</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2181842345437721</v>
+        <v>0.2200842345437721</v>
       </c>
       <c r="C76">
-        <v>-535.0846009767059</v>
+        <v>-554.2333743253033</v>
       </c>
       <c r="D76">
-        <v>411.9737783165492</v>
+        <v>407.4825506340769</v>
       </c>
       <c r="E76">
-        <v>945.2038126807481</v>
+        <v>959.8613583468732</v>
       </c>
       <c r="F76">
-        <v>1084.658379293255</v>
+        <v>1099.31592495938</v>
       </c>
       <c r="G76">
         <v>137.6</v>
@@ -7519,37 +7519,37 @@
         <v>84.63</v>
       </c>
       <c r="M76">
-        <v>255.7624458373496</v>
+        <v>259.2186951054219</v>
       </c>
       <c r="N76">
-        <v>-171.1324458373496</v>
+        <v>-174.5886951054219</v>
       </c>
       <c r="O76">
-        <v>-54.76238266795187</v>
+        <v>-55.86838243373501</v>
       </c>
       <c r="P76">
-        <v>-116.3700631693977</v>
+        <v>-118.7203126716869</v>
       </c>
       <c r="Q76">
-        <v>-79.47006316939772</v>
+        <v>-81.82031267168688</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2391094304800864</v>
+        <v>0.2468418076992899</v>
       </c>
       <c r="T76">
-        <v>2.51946991064194</v>
+        <v>2.620248707067618</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1058857562584554</v>
+        <v>0.1044739461750093</v>
       </c>
       <c r="W76">
-        <v>0.2108321386742562</v>
+        <v>0.2111650434919328</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3308929883076731</v>
+        <v>0.3264810817969042</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2200842345437721</v>
+        <v>0.2219842345437721</v>
       </c>
       <c r="C77">
-        <v>-554.2333743253033</v>
+        <v>-573.2852793857837</v>
       </c>
       <c r="D77">
-        <v>407.4825506340769</v>
+        <v>403.0881912397216</v>
       </c>
       <c r="E77">
-        <v>959.8613583468732</v>
+        <v>974.5189040129983</v>
       </c>
       <c r="F77">
-        <v>1099.31592495938</v>
+        <v>1113.973470625505</v>
       </c>
       <c r="G77">
         <v>137.6</v>
@@ -7601,37 +7601,37 @@
         <v>84.63</v>
       </c>
       <c r="M77">
-        <v>259.2186951054219</v>
+        <v>262.6749443734942</v>
       </c>
       <c r="N77">
-        <v>-174.5886951054219</v>
+        <v>-178.0449443734942</v>
       </c>
       <c r="O77">
-        <v>-55.86838243373501</v>
+        <v>-56.97438219951813</v>
       </c>
       <c r="P77">
-        <v>-118.7203126716869</v>
+        <v>-121.070562173976</v>
       </c>
       <c r="Q77">
-        <v>-81.82031267168688</v>
+        <v>-84.17056217397604</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2468418076992899</v>
+        <v>0.2552185496867603</v>
       </c>
       <c r="T77">
-        <v>2.620248707067618</v>
+        <v>2.729425736528769</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1044739461750093</v>
+        <v>0.1030992889884961</v>
       </c>
       <c r="W77">
-        <v>0.2111650434919328</v>
+        <v>0.2114891876565126</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3264810817969042</v>
+        <v>0.3221852780890502</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2219842345437721</v>
+        <v>0.2238842345437721</v>
       </c>
       <c r="C78">
-        <v>-573.2852793857837</v>
+        <v>-592.2434166529425</v>
       </c>
       <c r="D78">
-        <v>403.0881912397216</v>
+        <v>398.7875996386879</v>
       </c>
       <c r="E78">
-        <v>974.5189040129983</v>
+        <v>989.1764496791234</v>
       </c>
       <c r="F78">
-        <v>1113.973470625505</v>
+        <v>1128.63101629163</v>
       </c>
       <c r="G78">
         <v>137.6</v>
@@ -7683,37 +7683,37 @@
         <v>84.63</v>
       </c>
       <c r="M78">
-        <v>262.6749443734942</v>
+        <v>266.1311936415665</v>
       </c>
       <c r="N78">
-        <v>-178.0449443734942</v>
+        <v>-181.5011936415665</v>
       </c>
       <c r="O78">
-        <v>-56.97438219951813</v>
+        <v>-58.08038196530128</v>
       </c>
       <c r="P78">
-        <v>-121.070562173976</v>
+        <v>-123.4208116762652</v>
       </c>
       <c r="Q78">
-        <v>-84.17056217397604</v>
+        <v>-86.5208116762652</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2552185496867603</v>
+        <v>0.2643237040209673</v>
       </c>
       <c r="T78">
-        <v>2.729425736528769</v>
+        <v>2.848096420725672</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1030992889884961</v>
+        <v>0.1017603371834506</v>
       </c>
       <c r="W78">
-        <v>0.2114891876565126</v>
+        <v>0.2118049124921423</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3221852780890502</v>
+        <v>0.3180010536982832</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2238842345437721</v>
+        <v>0.2257842345437721</v>
       </c>
       <c r="C79">
-        <v>-592.2434166529425</v>
+        <v>-611.1107557003278</v>
       </c>
       <c r="D79">
-        <v>398.7875996386879</v>
+        <v>394.5778062574278</v>
       </c>
       <c r="E79">
-        <v>989.1764496791234</v>
+        <v>1003.833995345248</v>
       </c>
       <c r="F79">
-        <v>1128.63101629163</v>
+        <v>1143.288561957756</v>
       </c>
       <c r="G79">
         <v>137.6</v>
@@ -7765,37 +7765,37 @@
         <v>84.63</v>
       </c>
       <c r="M79">
-        <v>266.1311936415665</v>
+        <v>269.5874429096388</v>
       </c>
       <c r="N79">
-        <v>-181.5011936415665</v>
+        <v>-184.9574429096388</v>
       </c>
       <c r="O79">
-        <v>-58.08038196530128</v>
+        <v>-59.1863817310844</v>
       </c>
       <c r="P79">
-        <v>-123.4208116762652</v>
+        <v>-125.7710611785544</v>
       </c>
       <c r="Q79">
-        <v>-86.5208116762652</v>
+        <v>-88.87106117855436</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2643237040209673</v>
+        <v>0.274256599658284</v>
       </c>
       <c r="T79">
-        <v>2.848096420725672</v>
+        <v>2.977555348940475</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1017603371834506</v>
+        <v>0.1004557174759705</v>
       </c>
       <c r="W79">
-        <v>0.2118049124921423</v>
+        <v>0.2121125418191662</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3180010536982832</v>
+        <v>0.3139241171124079</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2257842345437721</v>
+        <v>0.2276842345437721</v>
       </c>
       <c r="C80">
-        <v>-611.1107557003278</v>
+        <v>-629.8901420183905</v>
       </c>
       <c r="D80">
-        <v>394.5778062574278</v>
+        <v>390.4559656054901</v>
       </c>
       <c r="E80">
-        <v>1003.833995345248</v>
+        <v>1018.491541011374</v>
       </c>
       <c r="F80">
-        <v>1143.288561957756</v>
+        <v>1157.946107623881</v>
       </c>
       <c r="G80">
         <v>137.6</v>
@@ -7847,37 +7847,37 @@
         <v>84.63</v>
       </c>
       <c r="M80">
-        <v>269.5874429096388</v>
+        <v>273.0436921777111</v>
       </c>
       <c r="N80">
-        <v>-184.9574429096388</v>
+        <v>-188.4136921777111</v>
       </c>
       <c r="O80">
-        <v>-59.1863817310844</v>
+        <v>-60.29238149686755</v>
       </c>
       <c r="P80">
-        <v>-125.7710611785544</v>
+        <v>-128.1213106808435</v>
       </c>
       <c r="Q80">
-        <v>-88.87106117855436</v>
+        <v>-91.22131068084352</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.274256599658284</v>
+        <v>0.2851354853562975</v>
       </c>
       <c r="T80">
-        <v>2.977555348940475</v>
+        <v>3.119343698890022</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1004557174759705</v>
+        <v>0.09918412611551518</v>
       </c>
       <c r="W80">
-        <v>0.2121125418191662</v>
+        <v>0.2124123830619615</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3139241171124079</v>
+        <v>0.3099503941109849</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2276842345437721</v>
+        <v>0.2295842345437721</v>
       </c>
       <c r="C81">
-        <v>-629.8901420183905</v>
+        <v>-648.5843034284725</v>
       </c>
       <c r="D81">
-        <v>390.4559656054901</v>
+        <v>386.4193498615332</v>
       </c>
       <c r="E81">
-        <v>1018.491541011374</v>
+        <v>1033.149086677499</v>
       </c>
       <c r="F81">
-        <v>1157.946107623881</v>
+        <v>1172.603653290006</v>
       </c>
       <c r="G81">
         <v>137.6</v>
@@ -7929,37 +7929,37 @@
         <v>84.63</v>
       </c>
       <c r="M81">
-        <v>273.0436921777111</v>
+        <v>276.4999414457833</v>
       </c>
       <c r="N81">
-        <v>-188.4136921777111</v>
+        <v>-191.8699414457834</v>
       </c>
       <c r="O81">
-        <v>-60.29238149686755</v>
+        <v>-61.39838126265067</v>
       </c>
       <c r="P81">
-        <v>-128.1213106808435</v>
+        <v>-130.4715601831327</v>
       </c>
       <c r="Q81">
-        <v>-91.22131068084352</v>
+        <v>-93.57156018313268</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2851354853562975</v>
+        <v>0.2971022596241124</v>
       </c>
       <c r="T81">
-        <v>3.119343698890022</v>
+        <v>3.275310883834524</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.09918412611551518</v>
+        <v>0.09794432453907125</v>
       </c>
       <c r="W81">
-        <v>0.2124123830619615</v>
+        <v>0.212704728273687</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3099503941109849</v>
+        <v>0.3060760141845976</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2295842345437721</v>
+        <v>0.2314842345437721</v>
       </c>
       <c r="C82">
-        <v>-648.5843034284725</v>
+        <v>-667.1958561030053</v>
       </c>
       <c r="D82">
-        <v>386.4193498615332</v>
+        <v>382.4653428531254</v>
       </c>
       <c r="E82">
-        <v>1033.149086677499</v>
+        <v>1047.806632343624</v>
       </c>
       <c r="F82">
-        <v>1172.603653290006</v>
+        <v>1187.261198956131</v>
       </c>
       <c r="G82">
         <v>137.6</v>
@@ -8011,37 +8011,37 @@
         <v>84.63</v>
       </c>
       <c r="M82">
-        <v>276.4999414457833</v>
+        <v>279.9561907138557</v>
       </c>
       <c r="N82">
-        <v>-191.8699414457834</v>
+        <v>-195.3261907138557</v>
       </c>
       <c r="O82">
-        <v>-61.39838126265067</v>
+        <v>-62.50438102843382</v>
       </c>
       <c r="P82">
-        <v>-130.4715601831327</v>
+        <v>-132.8218096854219</v>
       </c>
       <c r="Q82">
-        <v>-93.57156018313268</v>
+        <v>-95.92180968542186</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2971022596241124</v>
+        <v>0.3103286943411709</v>
       </c>
       <c r="T82">
-        <v>3.275310883834524</v>
+        <v>3.447695667194235</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09794432453907125</v>
+        <v>0.09673513534723084</v>
       </c>
       <c r="W82">
-        <v>0.212704728273687</v>
+        <v>0.212989855085123</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3060760141845976</v>
+        <v>0.3022972979600964</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2314842345437721</v>
+        <v>0.2333842345437721</v>
       </c>
       <c r="C83">
-        <v>-667.1958561030053</v>
+        <v>-685.7273102198504</v>
       </c>
       <c r="D83">
-        <v>382.4653428531254</v>
+        <v>378.5914344024055</v>
       </c>
       <c r="E83">
-        <v>1047.806632343624</v>
+        <v>1062.464178009749</v>
       </c>
       <c r="F83">
-        <v>1187.261198956131</v>
+        <v>1201.918744622256</v>
       </c>
       <c r="G83">
         <v>137.6</v>
@@ -8093,37 +8093,37 @@
         <v>84.63</v>
       </c>
       <c r="M83">
-        <v>279.9561907138557</v>
+        <v>283.4124399819279</v>
       </c>
       <c r="N83">
-        <v>-195.3261907138557</v>
+        <v>-198.782439981928</v>
       </c>
       <c r="O83">
-        <v>-62.50438102843382</v>
+        <v>-63.61038079421694</v>
       </c>
       <c r="P83">
-        <v>-132.8218096854219</v>
+        <v>-135.172059187711</v>
       </c>
       <c r="Q83">
-        <v>-95.92180968542186</v>
+        <v>-98.27205918771099</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3103286943411709</v>
+        <v>0.3250247329156805</v>
       </c>
       <c r="T83">
-        <v>3.447695667194235</v>
+        <v>3.639234315371693</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.09673513534723084</v>
+        <v>0.09555543857470365</v>
       </c>
       <c r="W83">
-        <v>0.212989855085123</v>
+        <v>0.2132680275840849</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3022972979600964</v>
+        <v>0.2986107455459489</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2333842345437721</v>
+        <v>0.2352842345437721</v>
       </c>
       <c r="C84">
-        <v>-685.7273102198504</v>
+        <v>-704.1810752764512</v>
       </c>
       <c r="D84">
-        <v>378.5914344024055</v>
+        <v>374.7952150119297</v>
       </c>
       <c r="E84">
-        <v>1062.464178009749</v>
+        <v>1077.121723675874</v>
       </c>
       <c r="F84">
-        <v>1201.918744622256</v>
+        <v>1216.576290288381</v>
       </c>
       <c r="G84">
         <v>137.6</v>
@@ -8175,37 +8175,37 @@
         <v>84.63</v>
       </c>
       <c r="M84">
-        <v>283.4124399819279</v>
+        <v>286.8686892500002</v>
       </c>
       <c r="N84">
-        <v>-198.782439981928</v>
+        <v>-202.2386892500002</v>
       </c>
       <c r="O84">
-        <v>-63.61038079421694</v>
+        <v>-64.71638056000008</v>
       </c>
       <c r="P84">
-        <v>-135.172059187711</v>
+        <v>-137.5223086900002</v>
       </c>
       <c r="Q84">
-        <v>-98.27205918771099</v>
+        <v>-100.6223086900002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3250247329156805</v>
+        <v>0.3414497172048382</v>
       </c>
       <c r="T84">
-        <v>3.639234315371693</v>
+        <v>3.853306922158264</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.09555543857470365</v>
+        <v>0.0944041682304301</v>
       </c>
       <c r="W84">
-        <v>0.2132680275840849</v>
+        <v>0.2135394971312646</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2986107455459489</v>
+        <v>0.2950130257200941</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2352842345437721</v>
+        <v>0.2371842345437721</v>
       </c>
       <c r="C85">
-        <v>-704.1810752764512</v>
+        <v>-722.5594650874467</v>
       </c>
       <c r="D85">
-        <v>374.7952150119297</v>
+        <v>371.0743708670594</v>
       </c>
       <c r="E85">
-        <v>1077.121723675874</v>
+        <v>1091.779269341999</v>
       </c>
       <c r="F85">
-        <v>1216.576290288381</v>
+        <v>1231.233835954506</v>
       </c>
       <c r="G85">
         <v>137.6</v>
@@ -8257,37 +8257,37 @@
         <v>84.63</v>
       </c>
       <c r="M85">
-        <v>286.8686892500002</v>
+        <v>290.3249385180725</v>
       </c>
       <c r="N85">
-        <v>-202.2386892500002</v>
+        <v>-205.6949385180725</v>
       </c>
       <c r="O85">
-        <v>-64.71638056000008</v>
+        <v>-65.82238032578321</v>
       </c>
       <c r="P85">
-        <v>-137.5223086900002</v>
+        <v>-139.8725581922893</v>
       </c>
       <c r="Q85">
-        <v>-100.6223086900002</v>
+        <v>-102.9725581922893</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3414497172048382</v>
+        <v>0.3599278245301405</v>
       </c>
       <c r="T85">
-        <v>3.853306922158264</v>
+        <v>4.094138604793155</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0944041682304301</v>
+        <v>0.09328030908482975</v>
       </c>
       <c r="W85">
-        <v>0.2135394971312646</v>
+        <v>0.2138045031177971</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2950130257200941</v>
+        <v>0.2915009658900929</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2371842345437721</v>
+        <v>0.2390842345437721</v>
       </c>
       <c r="C86">
-        <v>-722.5594650874465</v>
+        <v>-740.8647024875175</v>
       </c>
       <c r="D86">
-        <v>371.0743708670594</v>
+        <v>367.4266791331134</v>
       </c>
       <c r="E86">
-        <v>1091.779269341999</v>
+        <v>1106.436815008124</v>
       </c>
       <c r="F86">
-        <v>1231.233835954506</v>
+        <v>1245.891381620631</v>
       </c>
       <c r="G86">
         <v>137.6</v>
@@ -8339,37 +8339,37 @@
         <v>84.63</v>
       </c>
       <c r="M86">
-        <v>290.3249385180725</v>
+        <v>293.7811877861448</v>
       </c>
       <c r="N86">
-        <v>-205.6949385180725</v>
+        <v>-209.1511877861448</v>
       </c>
       <c r="O86">
-        <v>-65.8223803257832</v>
+        <v>-66.92838009156632</v>
       </c>
       <c r="P86">
-        <v>-139.8725581922893</v>
+        <v>-142.2228076945784</v>
       </c>
       <c r="Q86">
-        <v>-102.9725581922893</v>
+        <v>-105.3228076945784</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3599278245301404</v>
+        <v>0.3808696794988164</v>
       </c>
       <c r="T86">
-        <v>4.094138604793153</v>
+        <v>4.367081178446029</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09328030908482976</v>
+        <v>0.09218289368383177</v>
       </c>
       <c r="W86">
-        <v>0.2138045031177971</v>
+        <v>0.2140632736693525</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.291500965890093</v>
+        <v>0.2880715427619743</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2390842345437721</v>
+        <v>0.2409842345437721</v>
       </c>
       <c r="C87">
-        <v>-740.8647024875175</v>
+        <v>-759.0989237595628</v>
       </c>
       <c r="D87">
-        <v>367.4266791331134</v>
+        <v>363.8500035271932</v>
       </c>
       <c r="E87">
-        <v>1106.436815008124</v>
+        <v>1121.094360674249</v>
       </c>
       <c r="F87">
-        <v>1245.891381620631</v>
+        <v>1260.548927286756</v>
       </c>
       <c r="G87">
         <v>137.6</v>
@@ -8421,37 +8421,37 @@
         <v>84.63</v>
       </c>
       <c r="M87">
-        <v>293.7811877861448</v>
+        <v>297.2374370542171</v>
       </c>
       <c r="N87">
-        <v>-209.1511877861448</v>
+        <v>-212.6074370542171</v>
       </c>
       <c r="O87">
-        <v>-66.92838009156632</v>
+        <v>-68.03437985734946</v>
       </c>
       <c r="P87">
-        <v>-142.2228076945784</v>
+        <v>-144.5730571968676</v>
       </c>
       <c r="Q87">
-        <v>-105.3228076945784</v>
+        <v>-107.6730571968676</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3808696794988164</v>
+        <v>0.4048032280344462</v>
       </c>
       <c r="T87">
-        <v>4.367081178446029</v>
+        <v>4.679015548335032</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.09218289368383177</v>
+        <v>0.09111099957122906</v>
       </c>
       <c r="W87">
-        <v>0.2140632736693525</v>
+        <v>0.2143160263011042</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2880715427619743</v>
+        <v>0.2847218736600908</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2409842345437721</v>
+        <v>0.2428842345437721</v>
       </c>
       <c r="C88">
-        <v>-759.0989237595628</v>
+        <v>-777.2641828067302</v>
       </c>
       <c r="D88">
-        <v>363.8500035271932</v>
+        <v>360.3422901461508</v>
       </c>
       <c r="E88">
-        <v>1121.094360674249</v>
+        <v>1135.751906340374</v>
       </c>
       <c r="F88">
-        <v>1260.548927286756</v>
+        <v>1275.206472952881</v>
       </c>
       <c r="G88">
         <v>137.6</v>
@@ -8503,37 +8503,37 @@
         <v>84.63</v>
       </c>
       <c r="M88">
-        <v>297.2374370542171</v>
+        <v>300.6936863222894</v>
       </c>
       <c r="N88">
-        <v>-212.6074370542171</v>
+        <v>-216.0636863222894</v>
       </c>
       <c r="O88">
-        <v>-68.03437985734946</v>
+        <v>-69.1403796231326</v>
       </c>
       <c r="P88">
-        <v>-144.5730571968676</v>
+        <v>-146.9233066991567</v>
       </c>
       <c r="Q88">
-        <v>-107.6730571968676</v>
+        <v>-110.0233066991567</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4048032280344462</v>
+        <v>0.4324188609601727</v>
       </c>
       <c r="T88">
-        <v>4.679015548335032</v>
+        <v>5.03893982128388</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09111099957122906</v>
+        <v>0.09006374670259426</v>
       </c>
       <c r="W88">
-        <v>0.2143160263011042</v>
+        <v>0.2145629685275283</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2847218736600908</v>
+        <v>0.2814492084456071</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2428842345437721</v>
+        <v>0.2447842345437721</v>
       </c>
       <c r="C89">
-        <v>-777.2641828067302</v>
+        <v>-795.3624550854307</v>
       </c>
       <c r="D89">
-        <v>360.3422901461508</v>
+        <v>356.9015635335755</v>
       </c>
       <c r="E89">
-        <v>1135.751906340374</v>
+        <v>1150.409452006499</v>
       </c>
       <c r="F89">
-        <v>1275.206472952881</v>
+        <v>1289.864018619006</v>
       </c>
       <c r="G89">
         <v>137.6</v>
@@ -8585,37 +8585,37 @@
         <v>84.63</v>
       </c>
       <c r="M89">
-        <v>300.6936863222894</v>
+        <v>304.1499355903617</v>
       </c>
       <c r="N89">
-        <v>-216.0636863222894</v>
+        <v>-219.5199355903617</v>
       </c>
       <c r="O89">
-        <v>-69.1403796231326</v>
+        <v>-70.24637938891574</v>
       </c>
       <c r="P89">
-        <v>-146.9233066991567</v>
+        <v>-149.273556201446</v>
       </c>
       <c r="Q89">
-        <v>-110.0233066991567</v>
+        <v>-112.373556201446</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4324188609601727</v>
+        <v>0.4646370993735206</v>
       </c>
       <c r="T89">
-        <v>5.03893982128388</v>
+        <v>5.458851473057538</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.09006374670259426</v>
+        <v>0.0890402950355193</v>
       </c>
       <c r="W89">
-        <v>0.2145629685275283</v>
+        <v>0.2148042984306245</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2814492084456071</v>
+        <v>0.2782509219859979</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2447842345437721</v>
+        <v>0.2466842345437721</v>
       </c>
       <c r="C90">
-        <v>-795.3624550854307</v>
+        <v>-813.3956413151564</v>
       </c>
       <c r="D90">
-        <v>356.9015635335755</v>
+        <v>353.5259229699749</v>
       </c>
       <c r="E90">
-        <v>1150.409452006499</v>
+        <v>1165.066997672624</v>
       </c>
       <c r="F90">
-        <v>1289.864018619006</v>
+        <v>1304.521564285131</v>
       </c>
       <c r="G90">
         <v>137.6</v>
@@ -8667,37 +8667,37 @@
         <v>84.63</v>
       </c>
       <c r="M90">
-        <v>304.1499355903617</v>
+        <v>307.6061848584339</v>
       </c>
       <c r="N90">
-        <v>-219.5199355903617</v>
+        <v>-222.976184858434</v>
       </c>
       <c r="O90">
-        <v>-70.24637938891574</v>
+        <v>-71.35237915469887</v>
       </c>
       <c r="P90">
-        <v>-149.273556201446</v>
+        <v>-151.6238057037351</v>
       </c>
       <c r="Q90">
-        <v>-112.373556201446</v>
+        <v>-114.7238057037351</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4646370993735206</v>
+        <v>0.502713199316568</v>
       </c>
       <c r="T90">
-        <v>5.458851473057538</v>
+        <v>5.955110697880952</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0890402950355193</v>
+        <v>0.08803984228231122</v>
       </c>
       <c r="W90">
-        <v>0.2148042984306245</v>
+        <v>0.215040205189831</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2782509219859979</v>
+        <v>0.2751245071322226</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2466842345437721</v>
+        <v>0.2485842345437721</v>
       </c>
       <c r="C91">
-        <v>-813.3956413151564</v>
+        <v>-831.3655709797422</v>
       </c>
       <c r="D91">
-        <v>353.5259229699749</v>
+        <v>350.2135389715142</v>
       </c>
       <c r="E91">
-        <v>1165.066997672624</v>
+        <v>1179.724543338749</v>
       </c>
       <c r="F91">
-        <v>1304.521564285131</v>
+        <v>1319.179109951256</v>
       </c>
       <c r="G91">
         <v>137.6</v>
@@ -8749,37 +8749,37 @@
         <v>84.63</v>
       </c>
       <c r="M91">
-        <v>307.6061848584339</v>
+        <v>311.0624341265063</v>
       </c>
       <c r="N91">
-        <v>-222.976184858434</v>
+        <v>-226.4324341265063</v>
       </c>
       <c r="O91">
-        <v>-71.35237915469887</v>
+        <v>-72.45837892048201</v>
       </c>
       <c r="P91">
-        <v>-151.6238057037351</v>
+        <v>-153.9740552060243</v>
       </c>
       <c r="Q91">
-        <v>-114.7238057037351</v>
+        <v>-117.0740552060243</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.502713199316568</v>
+        <v>0.5484045192482248</v>
       </c>
       <c r="T91">
-        <v>5.955110697880952</v>
+        <v>6.550621767669047</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08803984228231122</v>
+        <v>0.08706162181250778</v>
       </c>
       <c r="W91">
-        <v>0.215040205189831</v>
+        <v>0.2152708695766107</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2751245071322226</v>
+        <v>0.2720675681640867</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2485842345437721</v>
+        <v>0.2504842345437721</v>
       </c>
       <c r="C92">
-        <v>-831.3655709797422</v>
+        <v>-849.2740056336248</v>
       </c>
       <c r="D92">
-        <v>350.2135389715142</v>
+        <v>346.9626499837566</v>
       </c>
       <c r="E92">
-        <v>1179.724543338749</v>
+        <v>1194.382089004874</v>
       </c>
       <c r="F92">
-        <v>1319.179109951256</v>
+        <v>1333.836655617381</v>
       </c>
       <c r="G92">
         <v>137.6</v>
@@ -8831,37 +8831,37 @@
         <v>84.63</v>
       </c>
       <c r="M92">
-        <v>311.0624341265063</v>
+        <v>314.5186833945785</v>
       </c>
       <c r="N92">
-        <v>-226.4324341265063</v>
+        <v>-229.8886833945785</v>
       </c>
       <c r="O92">
-        <v>-72.45837892048201</v>
+        <v>-73.56437868626514</v>
       </c>
       <c r="P92">
-        <v>-153.9740552060243</v>
+        <v>-156.3243047083134</v>
       </c>
       <c r="Q92">
-        <v>-117.0740552060243</v>
+        <v>-119.4243047083134</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5484045192482248</v>
+        <v>0.6042494658313607</v>
       </c>
       <c r="T92">
-        <v>6.550621767669047</v>
+        <v>7.278468630743385</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08706162181250778</v>
+        <v>0.08610490069368901</v>
       </c>
       <c r="W92">
-        <v>0.2152708695766107</v>
+        <v>0.2154964644164281</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2720675681640867</v>
+        <v>0.2690778146677781</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2504842345437721</v>
+        <v>0.2523842345437721</v>
       </c>
       <c r="C93">
-        <v>-849.2740056336248</v>
+        <v>-867.1226420256467</v>
       </c>
       <c r="D93">
-        <v>346.9626499837566</v>
+        <v>343.7715592578598</v>
       </c>
       <c r="E93">
-        <v>1194.382089004874</v>
+        <v>1209.039634670999</v>
       </c>
       <c r="F93">
-        <v>1333.836655617381</v>
+        <v>1348.494201283507</v>
       </c>
       <c r="G93">
         <v>137.6</v>
@@ -8913,37 +8913,37 @@
         <v>84.63</v>
       </c>
       <c r="M93">
-        <v>314.5186833945785</v>
+        <v>317.9749326626509</v>
       </c>
       <c r="N93">
-        <v>-229.8886833945785</v>
+        <v>-233.3449326626509</v>
       </c>
       <c r="O93">
-        <v>-73.56437868626514</v>
+        <v>-74.67037845204828</v>
       </c>
       <c r="P93">
-        <v>-156.3243047083134</v>
+        <v>-158.6745542106026</v>
       </c>
       <c r="Q93">
-        <v>-119.4243047083134</v>
+        <v>-121.7745542106026</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6042494658313607</v>
+        <v>0.674055649060281</v>
       </c>
       <c r="T93">
-        <v>7.278468630743385</v>
+        <v>8.18827720958631</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08610490069368901</v>
+        <v>0.08516897786006193</v>
       </c>
       <c r="W93">
-        <v>0.2154964644164281</v>
+        <v>0.2157171550205974</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2690778146677781</v>
+        <v>0.2661530558126936</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2523842345437721</v>
+        <v>0.2542842345437721</v>
       </c>
       <c r="C94">
-        <v>-867.1226420256467</v>
+        <v>-884.9131150520553</v>
       </c>
       <c r="D94">
-        <v>343.7715592578598</v>
+        <v>340.6386318975763</v>
       </c>
       <c r="E94">
-        <v>1209.039634670999</v>
+        <v>1223.697180337125</v>
       </c>
       <c r="F94">
-        <v>1348.494201283507</v>
+        <v>1363.151746949632</v>
       </c>
       <c r="G94">
         <v>137.6</v>
@@ -8995,37 +8995,37 @@
         <v>84.63</v>
       </c>
       <c r="M94">
-        <v>317.9749326626509</v>
+        <v>321.4311819307231</v>
       </c>
       <c r="N94">
-        <v>-233.3449326626509</v>
+        <v>-236.8011819307231</v>
       </c>
       <c r="O94">
-        <v>-74.67037845204828</v>
+        <v>-75.77637821783141</v>
       </c>
       <c r="P94">
-        <v>-158.6745542106026</v>
+        <v>-161.0248037128918</v>
       </c>
       <c r="Q94">
-        <v>-121.7745542106026</v>
+        <v>-124.1248037128917</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.674055649060281</v>
+        <v>0.7638064560688927</v>
       </c>
       <c r="T94">
-        <v>8.18827720958631</v>
+        <v>9.35803109667007</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08516897786006193</v>
+        <v>0.08425318239920106</v>
       </c>
       <c r="W94">
-        <v>0.2157171550205974</v>
+        <v>0.2159330995902684</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2661530558126936</v>
+        <v>0.2632911949975033</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2542842345437721</v>
+        <v>0.2561842345437721</v>
       </c>
       <c r="C95">
-        <v>-884.9131150520553</v>
+        <v>-902.6470005494843</v>
       </c>
       <c r="D95">
-        <v>340.6386318975763</v>
+        <v>337.5622920662724</v>
       </c>
       <c r="E95">
-        <v>1223.697180337125</v>
+        <v>1238.35472600325</v>
       </c>
       <c r="F95">
-        <v>1363.151746949632</v>
+        <v>1377.809292615757</v>
       </c>
       <c r="G95">
         <v>137.6</v>
@@ -9077,37 +9077,37 @@
         <v>84.63</v>
       </c>
       <c r="M95">
-        <v>321.4311819307231</v>
+        <v>324.8874311987955</v>
       </c>
       <c r="N95">
-        <v>-236.8011819307231</v>
+        <v>-240.2574311987955</v>
       </c>
       <c r="O95">
-        <v>-75.77637821783141</v>
+        <v>-76.88237798361455</v>
       </c>
       <c r="P95">
-        <v>-161.0248037128918</v>
+        <v>-163.3750532151809</v>
       </c>
       <c r="Q95">
-        <v>-124.1248037128917</v>
+        <v>-126.4750532151809</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7638064560688927</v>
+        <v>0.8834741987470418</v>
       </c>
       <c r="T95">
-        <v>9.35803109667007</v>
+        <v>10.91770294611509</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08425318239920106</v>
+        <v>0.08335687194814574</v>
       </c>
       <c r="W95">
-        <v>0.2159330995902684</v>
+        <v>0.2161444495946272</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2632911949975033</v>
+        <v>0.2604902248379554</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2561842345437721</v>
+        <v>0.2580842345437721</v>
       </c>
       <c r="C96">
-        <v>-902.6470005494843</v>
+        <v>-920.3258179379505</v>
       </c>
       <c r="D96">
-        <v>337.5622920662724</v>
+        <v>334.5410203439312</v>
       </c>
       <c r="E96">
-        <v>1238.35472600325</v>
+        <v>1253.012271669375</v>
       </c>
       <c r="F96">
-        <v>1377.809292615757</v>
+        <v>1392.466838281882</v>
       </c>
       <c r="G96">
         <v>137.6</v>
@@ -9159,37 +9159,37 @@
         <v>84.63</v>
       </c>
       <c r="M96">
-        <v>324.8874311987955</v>
+        <v>328.3436804668677</v>
       </c>
       <c r="N96">
-        <v>-240.2574311987955</v>
+        <v>-243.7136804668677</v>
       </c>
       <c r="O96">
-        <v>-76.88237798361455</v>
+        <v>-77.98837774939769</v>
       </c>
       <c r="P96">
-        <v>-163.3750532151809</v>
+        <v>-165.7253027174701</v>
       </c>
       <c r="Q96">
-        <v>-126.4750532151809</v>
+        <v>-128.8253027174701</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8834741987470418</v>
+        <v>1.051009038496451</v>
       </c>
       <c r="T96">
-        <v>10.91770294611509</v>
+        <v>13.10124353533811</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08335687194814574</v>
+        <v>0.08247943119079683</v>
       </c>
       <c r="W96">
-        <v>0.2161444495946272</v>
+        <v>0.2163513501252101</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2604902248379554</v>
+        <v>0.2577482224712401</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2580842345437721</v>
+        <v>0.2599842345437721</v>
       </c>
       <c r="C97">
-        <v>-920.3258179379505</v>
+        <v>-937.9510327231748</v>
       </c>
       <c r="D97">
-        <v>334.5410203439312</v>
+        <v>331.5733512248321</v>
       </c>
       <c r="E97">
-        <v>1253.012271669375</v>
+        <v>1267.6698173355</v>
       </c>
       <c r="F97">
-        <v>1392.466838281882</v>
+        <v>1407.124383948007</v>
       </c>
       <c r="G97">
         <v>137.6</v>
@@ -9241,37 +9241,37 @@
         <v>84.63</v>
       </c>
       <c r="M97">
-        <v>328.3436804668677</v>
+        <v>331.79992973494</v>
       </c>
       <c r="N97">
-        <v>-243.7136804668677</v>
+        <v>-247.16992973494</v>
       </c>
       <c r="O97">
-        <v>-77.98837774939769</v>
+        <v>-79.09437751518081</v>
       </c>
       <c r="P97">
-        <v>-165.7253027174701</v>
+        <v>-168.0755522197592</v>
       </c>
       <c r="Q97">
-        <v>-128.8253027174701</v>
+        <v>-131.1755522197592</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.051009038496451</v>
+        <v>1.302311298120564</v>
       </c>
       <c r="T97">
-        <v>13.10124353533811</v>
+        <v>16.37655441917265</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08247943119079683</v>
+        <v>0.08162027044922603</v>
       </c>
       <c r="W97">
-        <v>0.2163513501252101</v>
+        <v>0.2165539402280725</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2577482224712401</v>
+        <v>0.2550633451538313</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2599842345437721</v>
+        <v>0.2618842345437721</v>
       </c>
       <c r="C98">
-        <v>-937.9510327231745</v>
+        <v>-955.5240588668889</v>
       </c>
       <c r="D98">
-        <v>331.5733512248321</v>
+        <v>328.6578707472428</v>
       </c>
       <c r="E98">
-        <v>1267.6698173355</v>
+        <v>1282.327363001625</v>
       </c>
       <c r="F98">
-        <v>1407.124383948007</v>
+        <v>1421.781929614132</v>
       </c>
       <c r="G98">
         <v>137.6</v>
@@ -9323,37 +9323,37 @@
         <v>84.63</v>
       </c>
       <c r="M98">
-        <v>331.79992973494</v>
+        <v>335.2561790030123</v>
       </c>
       <c r="N98">
-        <v>-247.16992973494</v>
+        <v>-250.6261790030123</v>
       </c>
       <c r="O98">
-        <v>-79.09437751518081</v>
+        <v>-80.20037728096393</v>
       </c>
       <c r="P98">
-        <v>-168.0755522197592</v>
+        <v>-170.4258017220483</v>
       </c>
       <c r="Q98">
-        <v>-131.1755522197592</v>
+        <v>-133.5258017220483</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.302311298120561</v>
+        <v>1.721148397494081</v>
       </c>
       <c r="T98">
-        <v>16.3765544191726</v>
+        <v>21.83540589223013</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08162027044922603</v>
+        <v>0.08077882436212061</v>
       </c>
       <c r="W98">
-        <v>0.2165539402280725</v>
+        <v>0.216752353215412</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2550633451538313</v>
+        <v>0.2524338261316269</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2618842345437721</v>
+        <v>0.2637842345437721</v>
       </c>
       <c r="C99">
-        <v>-955.5240588668889</v>
+        <v>-973.0462610331812</v>
       </c>
       <c r="D99">
-        <v>328.6578707472428</v>
+        <v>325.7932142470756</v>
       </c>
       <c r="E99">
-        <v>1282.327363001625</v>
+        <v>1296.98490866775</v>
       </c>
       <c r="F99">
-        <v>1421.781929614132</v>
+        <v>1436.439475280257</v>
       </c>
       <c r="G99">
         <v>137.6</v>
@@ -9405,37 +9405,37 @@
         <v>84.63</v>
       </c>
       <c r="M99">
-        <v>335.2561790030123</v>
+        <v>338.7124282710845</v>
       </c>
       <c r="N99">
-        <v>-250.6261790030123</v>
+        <v>-254.0824282710846</v>
       </c>
       <c r="O99">
-        <v>-80.20037728096393</v>
+        <v>-81.30637704674706</v>
       </c>
       <c r="P99">
-        <v>-170.4258017220483</v>
+        <v>-172.7760512243375</v>
       </c>
       <c r="Q99">
-        <v>-133.5258017220483</v>
+        <v>-135.8760512243375</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.721148397494081</v>
+        <v>2.558822596241121</v>
       </c>
       <c r="T99">
-        <v>21.83540589223013</v>
+        <v>32.7531088383452</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08077882436212061</v>
+        <v>0.0799545506441398</v>
       </c>
       <c r="W99">
-        <v>0.216752353215412</v>
+        <v>0.2169467169581119</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2524338261316269</v>
+        <v>0.2498579707629369</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2637842345437721</v>
+        <v>0.2656842345437721</v>
       </c>
       <c r="C100">
-        <v>-973.0462610331812</v>
+        <v>-990.5189567183778</v>
       </c>
       <c r="D100">
-        <v>325.7932142470756</v>
+        <v>322.9780642280041</v>
       </c>
       <c r="E100">
-        <v>1296.98490866775</v>
+        <v>1311.642454333875</v>
       </c>
       <c r="F100">
-        <v>1436.439475280257</v>
+        <v>1451.097020946382</v>
       </c>
       <c r="G100">
         <v>137.6</v>
@@ -9487,37 +9487,37 @@
         <v>84.63</v>
       </c>
       <c r="M100">
-        <v>338.7124282710845</v>
+        <v>342.1686775391569</v>
       </c>
       <c r="N100">
-        <v>-254.0824282710846</v>
+        <v>-257.5386775391569</v>
       </c>
       <c r="O100">
-        <v>-81.30637704674706</v>
+        <v>-82.4123768125302</v>
       </c>
       <c r="P100">
-        <v>-172.7760512243375</v>
+        <v>-175.1263007266267</v>
       </c>
       <c r="Q100">
-        <v>-135.8760512243375</v>
+        <v>-138.2263007266267</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.558822596241121</v>
+        <v>5.071845192482242</v>
       </c>
       <c r="T100">
-        <v>32.7531088383452</v>
+        <v>65.5062176766904</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0799545506441398</v>
+        <v>0.07914692892046161</v>
       </c>
       <c r="W100">
-        <v>0.2169467169581119</v>
+        <v>0.2171371541605552</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2498579707629369</v>
+        <v>0.2473341528764426</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2656842345437721</v>
-      </c>
-      <c r="C101">
-        <v>-990.5189567183778</v>
-      </c>
-      <c r="D101">
-        <v>322.9780642280041</v>
-      </c>
-      <c r="E101">
-        <v>1311.642454333875</v>
-      </c>
-      <c r="F101">
-        <v>1451.097020946382</v>
-      </c>
-      <c r="G101">
-        <v>137.6</v>
-      </c>
-      <c r="H101">
-        <v>1326.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>121.53</v>
-      </c>
-      <c r="K101">
-        <v>36.9</v>
-      </c>
-      <c r="L101">
-        <v>84.63</v>
-      </c>
-      <c r="M101">
-        <v>342.1686775391569</v>
-      </c>
-      <c r="N101">
-        <v>-257.5386775391569</v>
-      </c>
-      <c r="O101">
-        <v>-82.4123768125302</v>
-      </c>
-      <c r="P101">
-        <v>-175.1263007266267</v>
-      </c>
-      <c r="Q101">
-        <v>-138.2263007266267</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.071845192482242</v>
-      </c>
-      <c r="T101">
-        <v>65.5062176766904</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07914692892046161</v>
-      </c>
-      <c r="W101">
-        <v>0.2171371541605552</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2473341528764426</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
